--- a/tools/excel_export/excel/achievements.xlsx
+++ b/tools/excel_export/excel/achievements.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="855" uniqueCount="286">
   <si>
     <t>id</t>
   </si>
@@ -73,16 +73,16 @@
     <t>成就组（**同一条成就的多档共用**，如 st_clear；程序按它归并成一条展示）</t>
   </si>
   <si>
-    <t>档位：1=铜 / 2=银 / 3=金（同一 group 内必须从 1 连续）</t>
+    <t>档位序号（**1 起、组内连续**；界面文案 = 「阶段N」，**档位数不限**：账号等级 20 档 / 收集类 6~7 档）</t>
   </si>
   <si>
     <t>分类（界面页签）</t>
   </si>
   <si>
-    <t>成就名（同一 group 三行写同一个名字）</t>
-  </si>
-  <si>
-    <t>成就描述（列表副标题，可换行 \n）</t>
+    <t>成就名（同一 group 的各行写同一个名字）</t>
+  </si>
+  <si>
+    <t>成就描述（**逐档可不同**，卡面显示的是「下一档」那一行；⚠ 卡面只有 2 行位置 ≈ ≤26 个汉字宽）</t>
   </si>
   <si>
     <t>图标资源路径（textures/achievements/&lt;group&gt;，不带扩展名）；空 = 回落占位图</t>
@@ -91,7 +91,7 @@
     <t>完成条件（程序按它把对局事件换算成进度；模式见 docs/成就系统设计.md §3.3）</t>
   </si>
   <si>
-    <t>条件参数（预留：如指定英雄/分类 id，留空 = 不限）</t>
+    <t>条件参数：`run_*` 型 = **门槛**（正整数：阶段数/等级/击杀数/金币/秒），其余类型留空（容器会对漏填/错填告警）</t>
   </si>
   <si>
     <t>目标数量（累加型 = 累计到这么多；峰值型 = 达到这么多），必须 &gt; 0</t>
@@ -121,12 +121,69 @@
     <t>指挥官之路</t>
   </si>
   <si>
-    <t>提升账号等级。</t>
+    <t>账号等级达到5级。</t>
   </si>
   <si>
     <t>level_reached</t>
   </si>
   <si>
+    <t>账号等级达到10级。</t>
+  </si>
+  <si>
+    <t>账号等级达到15级。</t>
+  </si>
+  <si>
+    <t>账号等级达到20级。</t>
+  </si>
+  <si>
+    <t>账号等级达到25级。</t>
+  </si>
+  <si>
+    <t>账号等级达到30级。</t>
+  </si>
+  <si>
+    <t>账号等级达到35级。</t>
+  </si>
+  <si>
+    <t>账号等级达到40级。</t>
+  </si>
+  <si>
+    <t>账号等级达到45级。</t>
+  </si>
+  <si>
+    <t>账号等级达到50级。</t>
+  </si>
+  <si>
+    <t>账号等级达到55级。</t>
+  </si>
+  <si>
+    <t>账号等级达到60级。</t>
+  </si>
+  <si>
+    <t>账号等级达到65级。</t>
+  </si>
+  <si>
+    <t>账号等级达到70级。</t>
+  </si>
+  <si>
+    <t>账号等级达到75级。</t>
+  </si>
+  <si>
+    <t>账号等级达到80级。</t>
+  </si>
+  <si>
+    <t>账号等级达到85级。</t>
+  </si>
+  <si>
+    <t>账号等级达到90级。</t>
+  </si>
+  <si>
+    <t>账号等级达到95级。</t>
+  </si>
+  <si>
+    <t>账号等级达到100级。</t>
+  </si>
+  <si>
     <t>hero_start_level</t>
   </si>
   <si>
@@ -136,10 +193,43 @@
     <t>英雄宗师</t>
   </si>
   <si>
-    <t>在单局中把英雄等级提升到指定等级。</t>
-  </si>
-  <si>
-    <t>hero_level</t>
+    <t>累计3局单局英雄等级达到5级。</t>
+  </si>
+  <si>
+    <t>run_hero_level</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>累计5局单局英雄等级达到10级。</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>累计8局单局英雄等级达到15级。</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>累计10局单局英雄等级达到20级。</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>累计15局单局英雄等级达到25级。</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>累计20局单局英雄等级达到30级。</t>
+  </si>
+  <si>
+    <t>30</t>
   </si>
   <si>
     <t>battle_exp_bonus</t>
@@ -151,24 +241,57 @@
     <t>步步高升</t>
   </si>
   <si>
-    <t>累计提升账号等级。</t>
+    <t>累计提升账号等级5次。</t>
   </si>
   <si>
     <t>level_up_count</t>
   </si>
   <si>
+    <t>累计提升账号等级10次。</t>
+  </si>
+  <si>
+    <t>累计提升账号等级20次。</t>
+  </si>
+  <si>
+    <t>累计提升账号等级30次。</t>
+  </si>
+  <si>
+    <t>累计提升账号等级50次。</t>
+  </si>
+  <si>
+    <t>累计提升账号等级70次。</t>
+  </si>
+  <si>
+    <t>累计提升账号等级99次。</t>
+  </si>
+  <si>
     <t>lv_login</t>
   </si>
   <si>
     <t>风雨无阻</t>
   </si>
   <si>
-    <t>连续登录游戏。</t>
+    <t>连续登录3天。</t>
   </si>
   <si>
     <t>login_streak</t>
   </si>
   <si>
+    <t>连续登录7天。</t>
+  </si>
+  <si>
+    <t>连续登录14天。</t>
+  </si>
+  <si>
+    <t>连续登录30天。</t>
+  </si>
+  <si>
+    <t>连续登录60天。</t>
+  </si>
+  <si>
+    <t>连续登录100天。</t>
+  </si>
+  <si>
     <t>st_clear</t>
   </si>
   <si>
@@ -178,12 +301,27 @@
     <t>百战之师</t>
   </si>
   <si>
-    <t>击败最终BOSS通关。</t>
+    <t>击败最终BOSS通关1次。</t>
   </si>
   <si>
     <t>victory</t>
   </si>
   <si>
+    <t>击败最终BOSS通关3次。</t>
+  </si>
+  <si>
+    <t>击败最终BOSS通关5次。</t>
+  </si>
+  <si>
+    <t>击败最终BOSS通关10次。</t>
+  </si>
+  <si>
+    <t>击败最终BOSS通关20次。</t>
+  </si>
+  <si>
+    <t>击败最终BOSS通关50次。</t>
+  </si>
+  <si>
     <t>run_start_gold</t>
   </si>
   <si>
@@ -193,10 +331,43 @@
     <t>战线推进</t>
   </si>
   <si>
-    <t>在单局中把战线推进到指定阶段。</t>
-  </si>
-  <si>
-    <t>stage_reached</t>
+    <t>累计3局把战线推进到第2阶段。</t>
+  </si>
+  <si>
+    <t>run_stage</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>累计5局把战线推进到第3阶段。</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>累计8局把战线推进到第4阶段。</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>累计12局把战线推进到第5阶段。</t>
+  </si>
+  <si>
+    <t>累计15局把战线推进到第6阶段。</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>累计18局把战线推进到第8阶段。</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>累计20局把战线推进到第10阶段。</t>
   </si>
   <si>
     <t>shop_option_plus</t>
@@ -208,24 +379,48 @@
     <t>毫发无伤</t>
   </si>
   <si>
-    <t>在英雄未受到任何伤害的情况下通关。</t>
+    <t>在未受到任何伤害的情况下通关1次。</t>
   </si>
   <si>
     <t>clear_no_damage</t>
   </si>
   <si>
+    <t>在未受到任何伤害的情况下通关3次。</t>
+  </si>
+  <si>
+    <t>在未受到任何伤害的情况下通关6次。</t>
+  </si>
+  <si>
+    <t>在未受到任何伤害的情况下通关10次。</t>
+  </si>
+  <si>
+    <t>在未受到任何伤害的情况下通关20次。</t>
+  </si>
+  <si>
     <t>st_speed</t>
   </si>
   <si>
     <t>闪电战</t>
   </si>
   <si>
-    <t>在最终BOSS出现后30秒内击败它并通关。</t>
+    <t>在最终BOSS出现后30秒内击败它，累计1次。</t>
   </si>
   <si>
     <t>clear_fast</t>
   </si>
   <si>
+    <t>在最终BOSS出现后30秒内击败它，累计3次。</t>
+  </si>
+  <si>
+    <t>在最终BOSS出现后30秒内击败它，累计6次。</t>
+  </si>
+  <si>
+    <t>在最终BOSS出现后30秒内击败它，累计10次。</t>
+  </si>
+  <si>
+    <t>在最终BOSS出现后30秒内击败它，累计20次。</t>
+  </si>
+  <si>
     <t>cb_kill</t>
   </si>
   <si>
@@ -235,12 +430,27 @@
     <t>万人斩</t>
   </si>
   <si>
-    <t>累计击败敌人。</t>
+    <t>累计击败3000名敌人。</t>
   </si>
   <si>
     <t>kill_enemies</t>
   </si>
   <si>
+    <t>累计击败12000名敌人。</t>
+  </si>
+  <si>
+    <t>累计击败30000名敌人。</t>
+  </si>
+  <si>
+    <t>累计击败60000名敌人。</t>
+  </si>
+  <si>
+    <t>累计击败100000名敌人。</t>
+  </si>
+  <si>
+    <t>累计击败160000名敌人。</t>
+  </si>
+  <si>
     <t>kill_buff_discount</t>
   </si>
   <si>
@@ -250,10 +460,43 @@
     <t>单局屠戮</t>
   </si>
   <si>
-    <t>在单局中击败指定数量的敌人。</t>
-  </si>
-  <si>
-    <t>kill_in_run</t>
+    <t>累计5局单局击杀达到250只。</t>
+  </si>
+  <si>
+    <t>run_kill</t>
+  </si>
+  <si>
+    <t>250</t>
+  </si>
+  <si>
+    <t>累计8局单局击杀达到600只。</t>
+  </si>
+  <si>
+    <t>600</t>
+  </si>
+  <si>
+    <t>累计10局单局击杀达到1000只。</t>
+  </si>
+  <si>
+    <t>1000</t>
+  </si>
+  <si>
+    <t>累计12局单局击杀达到1500只。</t>
+  </si>
+  <si>
+    <t>1500</t>
+  </si>
+  <si>
+    <t>累计15局单局击杀达到2500只。</t>
+  </si>
+  <si>
+    <t>2500</t>
+  </si>
+  <si>
+    <t>累计20局单局击杀达到4000只。</t>
+  </si>
+  <si>
+    <t>4000</t>
   </si>
   <si>
     <t>cb_damage</t>
@@ -262,12 +505,24 @@
     <t>伤害之王</t>
   </si>
   <si>
-    <t>累计造成伤害。</t>
+    <t>累计造成1000000点伤害。</t>
   </si>
   <si>
     <t>damage_dealt</t>
   </si>
   <si>
+    <t>累计造成3000000点伤害。</t>
+  </si>
+  <si>
+    <t>累计造成8000000点伤害。</t>
+  </si>
+  <si>
+    <t>累计造成18000000点伤害。</t>
+  </si>
+  <si>
+    <t>累计造成35000000点伤害。</t>
+  </si>
+  <si>
     <t>gold_gain_bonus</t>
   </si>
   <si>
@@ -277,24 +532,48 @@
     <t>暴击狂人</t>
   </si>
   <si>
-    <t>累计打出暴击。</t>
+    <t>累计打出500次暴击。</t>
   </si>
   <si>
     <t>crit_hits</t>
   </si>
   <si>
+    <t>累计打出2500次暴击。</t>
+  </si>
+  <si>
+    <t>累计打出8000次暴击。</t>
+  </si>
+  <si>
+    <t>累计打出20000次暴击。</t>
+  </si>
+  <si>
+    <t>累计打出45000次暴击。</t>
+  </si>
+  <si>
     <t>cb_games</t>
   </si>
   <si>
     <t>久经沙场</t>
   </si>
   <si>
-    <t>完成对局（胜负不限）。</t>
+    <t>完成对局10局（胜负不限）。</t>
   </si>
   <si>
     <t>play_games</t>
   </si>
   <si>
+    <t>完成对局30局（胜负不限）。</t>
+  </si>
+  <si>
+    <t>完成对局100局（胜负不限）。</t>
+  </si>
+  <si>
+    <t>完成对局300局（胜负不限）。</t>
+  </si>
+  <si>
+    <t>完成对局600局（胜负不限）。</t>
+  </si>
+  <si>
     <t>ec_earn</t>
   </si>
   <si>
@@ -304,12 +583,24 @@
     <t>富甲一方</t>
   </si>
   <si>
-    <t>在局内累计获得金币。</t>
+    <t>在局内累计获得20000金币。</t>
   </si>
   <si>
     <t>gold_earned</t>
   </si>
   <si>
+    <t>在局内累计获得100000金币。</t>
+  </si>
+  <si>
+    <t>在局内累计获得300000金币。</t>
+  </si>
+  <si>
+    <t>在局内累计获得600000金币。</t>
+  </si>
+  <si>
+    <t>在局内累计获得1000000金币。</t>
+  </si>
+  <si>
     <t>shop_draw_discount</t>
   </si>
   <si>
@@ -319,22 +610,58 @@
     <t>消费达人</t>
   </si>
   <si>
-    <t>在局内累计消耗金币。</t>
+    <t>在局内累计消耗15000金币。</t>
   </si>
   <si>
     <t>spend_gold</t>
   </si>
   <si>
+    <t>在局内累计消耗80000金币。</t>
+  </si>
+  <si>
+    <t>在局内累计消耗250000金币。</t>
+  </si>
+  <si>
+    <t>在局内累计消耗500000金币。</t>
+  </si>
+  <si>
+    <t>在局内累计消耗900000金币。</t>
+  </si>
+  <si>
     <t>ec_run_gold</t>
   </si>
   <si>
     <t>单局首富</t>
   </si>
   <si>
-    <t>在单局中持有指定数量的金币。</t>
-  </si>
-  <si>
-    <t>gold_in_run</t>
+    <t>累计3局单局持有300金币。</t>
+  </si>
+  <si>
+    <t>run_gold</t>
+  </si>
+  <si>
+    <t>300</t>
+  </si>
+  <si>
+    <t>累计5局单局持有600金币。</t>
+  </si>
+  <si>
+    <t>累计8局单局持有1200金币。</t>
+  </si>
+  <si>
+    <t>1200</t>
+  </si>
+  <si>
+    <t>累计12局单局持有2000金币。</t>
+  </si>
+  <si>
+    <t>2000</t>
+  </si>
+  <si>
+    <t>累计15局单局持有3500金币。</t>
+  </si>
+  <si>
+    <t>3500</t>
   </si>
   <si>
     <t>ec_draw</t>
@@ -343,12 +670,24 @@
     <t>抽卡成瘾</t>
   </si>
   <si>
-    <t>在肉鸽商店累计抽取。</t>
+    <t>在肉鸽商店累计抽取50次。</t>
   </si>
   <si>
     <t>draw_count</t>
   </si>
   <si>
+    <t>在肉鸽商店累计抽取250次。</t>
+  </si>
+  <si>
+    <t>在肉鸽商店累计抽取800次。</t>
+  </si>
+  <si>
+    <t>在肉鸽商店累计抽取1800次。</t>
+  </si>
+  <si>
+    <t>在肉鸽商店累计抽取3000次。</t>
+  </si>
+  <si>
     <t>ad_free_draw</t>
   </si>
   <si>
@@ -361,7 +700,7 @@
     <t>图鉴大师</t>
   </si>
   <si>
-    <t>收集局外遗物图鉴（共37件）。</t>
+    <t>收集局外遗物图鉴（共268件）。</t>
   </si>
   <si>
     <t>relic_collected</t>
@@ -376,7 +715,7 @@
     <t>药剂收藏家</t>
   </si>
   <si>
-    <t>在击杀商店购买过不同种类的Buff（共20种）。</t>
+    <t>在神器商店购买过不同种类的神器（共19种）。</t>
   </si>
   <si>
     <t>buff_types</t>
@@ -388,7 +727,7 @@
     <t>技能全通</t>
   </si>
   <si>
-    <t>抽到过不同种类的肉鸽技能（共30个）。</t>
+    <t>抽到过不同种类的肉鸽技能（共31个）。</t>
   </si>
   <si>
     <t>skills_picked</t>
@@ -400,12 +739,24 @@
     <t>淘宝专家</t>
   </si>
   <si>
-    <t>在局内累计获得遗物。</t>
+    <t>在局内累计获得100件遗物。</t>
   </si>
   <si>
     <t>relics_picked</t>
   </si>
   <si>
+    <t>在局内累计获得400件遗物。</t>
+  </si>
+  <si>
+    <t>在局内累计获得900件遗物。</t>
+  </si>
+  <si>
+    <t>在局内累计获得1800件遗物。</t>
+  </si>
+  <si>
+    <t>在局内累计获得3000件遗物。</t>
+  </si>
+  <si>
     <t>ch_norelic</t>
   </si>
   <si>
@@ -415,12 +766,24 @@
     <t>裸装勇士</t>
   </si>
   <si>
-    <t>不带任何遗物通关。</t>
+    <t>不带任何遗物通关1次。</t>
   </si>
   <si>
     <t>run_no_relic_clear</t>
   </si>
   <si>
+    <t>不带任何遗物通关3次。</t>
+  </si>
+  <si>
+    <t>不带任何遗物通关6次。</t>
+  </si>
+  <si>
+    <t>不带任何遗物通关10次。</t>
+  </si>
+  <si>
+    <t>不带任何遗物通关20次。</t>
+  </si>
+  <si>
     <t>relic_start_gift</t>
   </si>
   <si>
@@ -430,34 +793,82 @@
     <t>独门绝技</t>
   </si>
   <si>
-    <t>只使用1个技能槽通关。</t>
+    <t>只使用1个技能槽通关1次。</t>
   </si>
   <si>
     <t>clear_one_skill</t>
   </si>
   <si>
+    <t>只使用1个技能槽通关3次。</t>
+  </si>
+  <si>
+    <t>只使用1个技能槽通关6次。</t>
+  </si>
+  <si>
+    <t>只使用1个技能槽通关10次。</t>
+  </si>
+  <si>
+    <t>只使用1个技能槽通关20次。</t>
+  </si>
+  <si>
     <t>ch_lowhp</t>
   </si>
   <si>
     <t>残血英雄</t>
   </si>
   <si>
-    <t>在生命值低于10%时击败最终BOSS通关。</t>
+    <t>在生命值低于10%时击败最终BOSS通关1次。</t>
   </si>
   <si>
     <t>clear_low_hp</t>
   </si>
   <si>
+    <t>在生命值低于10%时击败最终BOSS通关3次。</t>
+  </si>
+  <si>
+    <t>在生命值低于10%时击败最终BOSS通关6次。</t>
+  </si>
+  <si>
+    <t>在生命值低于10%时击败最终BOSS通关10次。</t>
+  </si>
+  <si>
+    <t>在生命值低于10%时击败最终BOSS通关20次。</t>
+  </si>
+  <si>
     <t>ch_survive</t>
   </si>
   <si>
     <t>屹立不倒</t>
   </si>
   <si>
-    <t>在单局中坚持指定时长。</t>
-  </si>
-  <si>
-    <t>survive_time</t>
+    <t>累计3局单局存活达到300秒。</t>
+  </si>
+  <si>
+    <t>run_survive</t>
+  </si>
+  <si>
+    <t>累计5局单局存活达到600秒。</t>
+  </si>
+  <si>
+    <t>累计8局单局存活达到900秒。</t>
+  </si>
+  <si>
+    <t>900</t>
+  </si>
+  <si>
+    <t>累计10局单局存活达到1200秒。</t>
+  </si>
+  <si>
+    <t>累计12局单局存活达到1800秒。</t>
+  </si>
+  <si>
+    <t>1800</t>
+  </si>
+  <si>
+    <t>累计15局单局存活达到3000秒。</t>
+  </si>
+  <si>
+    <t>3000</t>
   </si>
 </sst>
 </file>
@@ -897,17 +1308,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O78"/>
+  <dimension ref="A1:O157"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="39.5" customWidth="1"/>
     <col min="2" max="2" width="35.5" customWidth="1"/>
-    <col min="3" max="3" width="27" customWidth="1"/>
+    <col min="3" max="3" width="50" customWidth="1"/>
     <col min="4" max="4" width="11" customWidth="1"/>
-    <col min="5" max="5" width="18.5" customWidth="1"/>
-    <col min="6" max="6" width="44" customWidth="1"/>
+    <col min="5" max="5" width="19.5" customWidth="1"/>
+    <col min="6" max="6" width="46" customWidth="1"/>
     <col min="7" max="8" width="37" customWidth="1"/>
-    <col min="9" max="9" width="24.5" customWidth="1"/>
+    <col min="9" max="9" width="54" customWidth="1"/>
     <col min="10" max="10" width="32" customWidth="1"/>
     <col min="11" max="11" width="33" customWidth="1"/>
     <col min="12" max="12" width="37" customWidth="1"/>
@@ -1085,7 +1496,7 @@
         <v>5</v>
       </c>
       <c r="K4" s="4">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="L4" s="4"/>
       <c r="M4" s="4"/>
@@ -1111,7 +1522,7 @@
         <v>35</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G5" s="4"/>
       <c r="H5" s="4" t="s">
@@ -1119,10 +1530,10 @@
       </c>
       <c r="I5" s="4"/>
       <c r="J5" s="4">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="K5" s="4">
-        <v>1200</v>
+        <v>35</v>
       </c>
       <c r="L5" s="4"/>
       <c r="M5" s="4"/>
@@ -1148,7 +1559,7 @@
         <v>35</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G6" s="4"/>
       <c r="H6" s="4" t="s">
@@ -1156,17 +1567,13 @@
       </c>
       <c r="I6" s="4"/>
       <c r="J6" s="4">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="K6" s="4">
-        <v>6000</v>
-      </c>
-      <c r="L6" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="M6" s="4">
-        <v>1</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="L6" s="4"/>
+      <c r="M6" s="4"/>
       <c r="N6" s="4"/>
       <c r="O6" s="4">
         <v>1</v>
@@ -1177,36 +1584,36 @@
         <v>3104</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="C7" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>34</v>
       </c>
       <c r="E7" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F7" s="4" t="s">
         <v>40</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>41</v>
       </c>
       <c r="G7" s="4"/>
       <c r="H7" s="4" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="I7" s="4"/>
       <c r="J7" s="4">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="K7" s="4">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="L7" s="4"/>
       <c r="M7" s="4"/>
       <c r="N7" s="4"/>
       <c r="O7" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
@@ -1214,36 +1621,36 @@
         <v>3105</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="C8" s="4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>34</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>41</v>
       </c>
       <c r="G8" s="4"/>
       <c r="H8" s="4" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="I8" s="4"/>
       <c r="J8" s="4">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K8" s="4">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="L8" s="4"/>
       <c r="M8" s="4"/>
       <c r="N8" s="4"/>
       <c r="O8" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
@@ -1251,40 +1658,36 @@
         <v>3106</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="C9" s="4">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>34</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G9" s="4"/>
       <c r="H9" s="4" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="I9" s="4"/>
       <c r="J9" s="4">
         <v>30</v>
       </c>
       <c r="K9" s="4">
-        <v>5000</v>
-      </c>
-      <c r="L9" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="M9" s="4">
-        <v>10</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="L9" s="4"/>
+      <c r="M9" s="4"/>
       <c r="N9" s="4"/>
       <c r="O9" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
@@ -1292,36 +1695,36 @@
         <v>3107</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="C10" s="4">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>34</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="G10" s="4"/>
       <c r="H10" s="4" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="I10" s="4"/>
       <c r="J10" s="4">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="K10" s="4">
-        <v>300</v>
+        <v>90</v>
       </c>
       <c r="L10" s="4"/>
       <c r="M10" s="4"/>
       <c r="N10" s="4"/>
       <c r="O10" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
@@ -1329,36 +1732,36 @@
         <v>3108</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="C11" s="4">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>34</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G11" s="4"/>
       <c r="H11" s="4" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="I11" s="4"/>
       <c r="J11" s="4">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="K11" s="4">
-        <v>1200</v>
+        <v>105</v>
       </c>
       <c r="L11" s="4"/>
       <c r="M11" s="4"/>
       <c r="N11" s="4"/>
       <c r="O11" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
@@ -1366,36 +1769,36 @@
         <v>3109</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="C12" s="4">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>34</v>
       </c>
       <c r="E12" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F12" s="4" t="s">
         <v>45</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>46</v>
       </c>
       <c r="G12" s="4"/>
       <c r="H12" s="4" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="I12" s="4"/>
       <c r="J12" s="4">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="K12" s="4">
-        <v>6000</v>
+        <v>125</v>
       </c>
       <c r="L12" s="4"/>
       <c r="M12" s="4"/>
       <c r="N12" s="4"/>
       <c r="O12" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
@@ -1403,36 +1806,36 @@
         <v>3110</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="C13" s="4">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>34</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G13" s="4"/>
       <c r="H13" s="4" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="I13" s="4"/>
       <c r="J13" s="4">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="K13" s="4">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="L13" s="4"/>
       <c r="M13" s="4"/>
       <c r="N13" s="4"/>
       <c r="O13" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
@@ -1440,36 +1843,36 @@
         <v>3111</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="C14" s="4">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>34</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="G14" s="4"/>
       <c r="H14" s="4" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="I14" s="4"/>
       <c r="J14" s="4">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="K14" s="4">
-        <v>800</v>
+        <v>180</v>
       </c>
       <c r="L14" s="4"/>
       <c r="M14" s="4"/>
       <c r="N14" s="4"/>
       <c r="O14" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
@@ -1477,67 +1880,67 @@
         <v>3112</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="C15" s="4">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>34</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G15" s="4"/>
       <c r="H15" s="4" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="I15" s="4"/>
       <c r="J15" s="4">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="K15" s="4">
-        <v>4000</v>
+        <v>215</v>
       </c>
       <c r="L15" s="4"/>
       <c r="M15" s="4"/>
       <c r="N15" s="4"/>
       <c r="O15" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
-        <v>3201</v>
+        <v>3113</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="C16" s="4">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="G16" s="4"/>
       <c r="H16" s="4" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="I16" s="4"/>
       <c r="J16" s="4">
-        <v>1</v>
+        <v>65</v>
       </c>
       <c r="K16" s="4">
-        <v>400</v>
+        <v>255</v>
       </c>
       <c r="L16" s="4"/>
       <c r="M16" s="4"/>
@@ -1548,33 +1951,33 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
-        <v>3202</v>
+        <v>3114</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="C17" s="4">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G17" s="4"/>
       <c r="H17" s="4" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="I17" s="4"/>
       <c r="J17" s="4">
-        <v>10</v>
+        <v>70</v>
       </c>
       <c r="K17" s="4">
-        <v>1500</v>
+        <v>305</v>
       </c>
       <c r="L17" s="4"/>
       <c r="M17" s="4"/>
@@ -1585,40 +1988,36 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="4">
-        <v>3203</v>
+        <v>3115</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="C18" s="4">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="G18" s="4"/>
       <c r="H18" s="4" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="I18" s="4"/>
       <c r="J18" s="4">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="K18" s="4">
-        <v>6000</v>
-      </c>
-      <c r="L18" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="M18" s="4">
-        <v>50</v>
-      </c>
+        <v>370</v>
+      </c>
+      <c r="L18" s="4"/>
+      <c r="M18" s="4"/>
       <c r="N18" s="4"/>
       <c r="O18" s="4">
         <v>1</v>
@@ -1626,596 +2025,608 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
-        <v>3204</v>
+        <v>3116</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="C19" s="4">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="G19" s="4"/>
       <c r="H19" s="4" t="s">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="I19" s="4"/>
       <c r="J19" s="4">
-        <v>3</v>
+        <v>80</v>
       </c>
       <c r="K19" s="4">
-        <v>300</v>
+        <v>440</v>
       </c>
       <c r="L19" s="4"/>
       <c r="M19" s="4"/>
       <c r="N19" s="4"/>
       <c r="O19" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="4">
-        <v>3205</v>
+        <v>3117</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="C20" s="4">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="D20" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F20" s="4" t="s">
         <v>53</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>60</v>
       </c>
       <c r="G20" s="4"/>
       <c r="H20" s="4" t="s">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="I20" s="4"/>
       <c r="J20" s="4">
-        <v>4</v>
+        <v>85</v>
       </c>
       <c r="K20" s="4">
-        <v>1000</v>
+        <v>525</v>
       </c>
       <c r="L20" s="4"/>
       <c r="M20" s="4"/>
       <c r="N20" s="4"/>
       <c r="O20" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
-        <v>3206</v>
+        <v>3118</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="C21" s="4">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="G21" s="4"/>
       <c r="H21" s="4" t="s">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="I21" s="4"/>
       <c r="J21" s="4">
-        <v>5</v>
+        <v>90</v>
       </c>
       <c r="K21" s="4">
-        <v>5000</v>
-      </c>
-      <c r="L21" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="M21" s="4">
-        <v>1</v>
-      </c>
+        <v>630</v>
+      </c>
+      <c r="L21" s="4"/>
+      <c r="M21" s="4"/>
       <c r="N21" s="4"/>
       <c r="O21" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
-        <v>3207</v>
+        <v>3119</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="C22" s="4">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>64</v>
+        <v>35</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="G22" s="4"/>
       <c r="H22" s="4" t="s">
-        <v>66</v>
+        <v>37</v>
       </c>
       <c r="I22" s="4"/>
       <c r="J22" s="4">
-        <v>1</v>
+        <v>95</v>
       </c>
       <c r="K22" s="4">
-        <v>500</v>
+        <v>750</v>
       </c>
       <c r="L22" s="4"/>
       <c r="M22" s="4"/>
       <c r="N22" s="4"/>
       <c r="O22" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="4">
-        <v>3208</v>
+        <v>3120</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="C23" s="4">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>64</v>
+        <v>35</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="G23" s="4"/>
       <c r="H23" s="4" t="s">
-        <v>66</v>
+        <v>37</v>
       </c>
       <c r="I23" s="4"/>
       <c r="J23" s="4">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="K23" s="4">
-        <v>1800</v>
-      </c>
-      <c r="L23" s="4"/>
-      <c r="M23" s="4"/>
+        <v>900</v>
+      </c>
+      <c r="L23" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="M23" s="4">
+        <v>1</v>
+      </c>
       <c r="N23" s="4"/>
       <c r="O23" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="4">
-        <v>3209</v>
+        <v>3121</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C24" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="G24" s="4"/>
       <c r="H24" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="I24" s="4"/>
+        <v>61</v>
+      </c>
+      <c r="I24" s="4" t="s">
+        <v>62</v>
+      </c>
       <c r="J24" s="4">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="K24" s="4">
-        <v>5000</v>
+        <v>60</v>
       </c>
       <c r="L24" s="4"/>
       <c r="M24" s="4"/>
       <c r="N24" s="4"/>
       <c r="O24" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="4">
-        <v>3210</v>
+        <v>3122</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="C25" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="G25" s="4"/>
       <c r="H25" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="I25" s="4"/>
+        <v>61</v>
+      </c>
+      <c r="I25" s="4" t="s">
+        <v>64</v>
+      </c>
       <c r="J25" s="4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K25" s="4">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="L25" s="4"/>
       <c r="M25" s="4"/>
       <c r="N25" s="4"/>
       <c r="O25" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="4">
-        <v>3211</v>
+        <v>3123</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="C26" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="G26" s="4"/>
       <c r="H26" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="I26" s="4"/>
+        <v>61</v>
+      </c>
+      <c r="I26" s="4" t="s">
+        <v>66</v>
+      </c>
       <c r="J26" s="4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K26" s="4">
-        <v>1800</v>
+        <v>160</v>
       </c>
       <c r="L26" s="4"/>
       <c r="M26" s="4"/>
       <c r="N26" s="4"/>
       <c r="O26" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="4">
-        <v>3212</v>
+        <v>3124</v>
       </c>
       <c r="B27" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C27" s="4">
+        <v>4</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F27" s="4" t="s">
         <v>67</v>
-      </c>
-      <c r="C27" s="4">
-        <v>3</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="E27" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="F27" s="4" t="s">
-        <v>69</v>
       </c>
       <c r="G27" s="4"/>
       <c r="H27" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="I27" s="4"/>
+        <v>61</v>
+      </c>
+      <c r="I27" s="4" t="s">
+        <v>68</v>
+      </c>
       <c r="J27" s="4">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="K27" s="4">
-        <v>5000</v>
+        <v>260</v>
       </c>
       <c r="L27" s="4"/>
       <c r="M27" s="4"/>
       <c r="N27" s="4"/>
       <c r="O27" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="4">
-        <v>3301</v>
+        <v>3125</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="C28" s="4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="G28" s="4"/>
       <c r="H28" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="I28" s="4"/>
+        <v>61</v>
+      </c>
+      <c r="I28" s="4" t="s">
+        <v>70</v>
+      </c>
       <c r="J28" s="4">
-        <v>500</v>
+        <v>15</v>
       </c>
       <c r="K28" s="4">
-        <v>250</v>
+        <v>430</v>
       </c>
       <c r="L28" s="4"/>
       <c r="M28" s="4"/>
       <c r="N28" s="4"/>
       <c r="O28" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="4">
-        <v>3302</v>
+        <v>3126</v>
       </c>
       <c r="B29" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C29" s="4">
+        <v>6</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F29" s="4" t="s">
         <v>71</v>
-      </c>
-      <c r="C29" s="4">
-        <v>2</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="E29" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="F29" s="4" t="s">
-        <v>74</v>
       </c>
       <c r="G29" s="4"/>
       <c r="H29" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="I29" s="4"/>
+        <v>61</v>
+      </c>
+      <c r="I29" s="4" t="s">
+        <v>72</v>
+      </c>
       <c r="J29" s="4">
-        <v>5000</v>
+        <v>20</v>
       </c>
       <c r="K29" s="4">
-        <v>1200</v>
-      </c>
-      <c r="L29" s="4"/>
-      <c r="M29" s="4"/>
+        <v>700</v>
+      </c>
+      <c r="L29" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="M29" s="4">
+        <v>10</v>
+      </c>
       <c r="N29" s="4"/>
       <c r="O29" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="4">
-        <v>3303</v>
+        <v>3127</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C30" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G30" s="4"/>
       <c r="H30" s="4" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I30" s="4"/>
       <c r="J30" s="4">
-        <v>30000</v>
+        <v>5</v>
       </c>
       <c r="K30" s="4">
-        <v>5000</v>
-      </c>
-      <c r="L30" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="M30" s="4">
-        <v>10</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="L30" s="4"/>
+      <c r="M30" s="4"/>
       <c r="N30" s="4"/>
       <c r="O30" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="4">
-        <v>3304</v>
+        <v>3128</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C31" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="E31" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="F31" s="4" t="s">
         <v>78</v>
-      </c>
-      <c r="F31" s="4" t="s">
-        <v>79</v>
       </c>
       <c r="G31" s="4"/>
       <c r="H31" s="4" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="I31" s="4"/>
       <c r="J31" s="4">
-        <v>120</v>
+        <v>10</v>
       </c>
       <c r="K31" s="4">
-        <v>250</v>
+        <v>65</v>
       </c>
       <c r="L31" s="4"/>
       <c r="M31" s="4"/>
       <c r="N31" s="4"/>
       <c r="O31" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="4">
-        <v>3305</v>
+        <v>3129</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C32" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="F32" s="4" t="s">
         <v>79</v>
       </c>
       <c r="G32" s="4"/>
       <c r="H32" s="4" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="I32" s="4"/>
       <c r="J32" s="4">
-        <v>250</v>
+        <v>20</v>
       </c>
       <c r="K32" s="4">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="L32" s="4"/>
       <c r="M32" s="4"/>
       <c r="N32" s="4"/>
       <c r="O32" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="4">
-        <v>3306</v>
+        <v>3130</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C33" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G33" s="4"/>
       <c r="H33" s="4" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="I33" s="4"/>
       <c r="J33" s="4">
-        <v>400</v>
+        <v>30</v>
       </c>
       <c r="K33" s="4">
-        <v>4000</v>
+        <v>180</v>
       </c>
       <c r="L33" s="4"/>
       <c r="M33" s="4"/>
       <c r="N33" s="4"/>
       <c r="O33" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="4">
-        <v>3307</v>
+        <v>3131</v>
       </c>
       <c r="B34" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C34" s="4">
+        <v>5</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="F34" s="4" t="s">
         <v>81</v>
-      </c>
-      <c r="C34" s="4">
-        <v>1</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="E34" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="F34" s="4" t="s">
-        <v>83</v>
       </c>
       <c r="G34" s="4"/>
       <c r="H34" s="4" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="I34" s="4"/>
       <c r="J34" s="4">
-        <v>50000</v>
+        <v>50</v>
       </c>
       <c r="K34" s="4">
-        <v>250</v>
+        <v>295</v>
       </c>
       <c r="L34" s="4"/>
       <c r="M34" s="4"/>
@@ -2226,33 +2637,33 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="4">
-        <v>3308</v>
+        <v>3132</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="C35" s="4">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="E35" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="F35" s="4" t="s">
         <v>82</v>
-      </c>
-      <c r="F35" s="4" t="s">
-        <v>83</v>
       </c>
       <c r="G35" s="4"/>
       <c r="H35" s="4" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="I35" s="4"/>
       <c r="J35" s="4">
-        <v>2000000</v>
+        <v>70</v>
       </c>
       <c r="K35" s="4">
-        <v>1200</v>
+        <v>485</v>
       </c>
       <c r="L35" s="4"/>
       <c r="M35" s="4"/>
@@ -2263,40 +2674,36 @@
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="4">
-        <v>3309</v>
+        <v>3133</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="C36" s="4">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="F36" s="4" t="s">
         <v>83</v>
       </c>
       <c r="G36" s="4"/>
       <c r="H36" s="4" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="I36" s="4"/>
       <c r="J36" s="4">
-        <v>20000000</v>
+        <v>99</v>
       </c>
       <c r="K36" s="4">
-        <v>8000</v>
-      </c>
-      <c r="L36" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="M36" s="4">
-        <v>10</v>
-      </c>
+        <v>800</v>
+      </c>
+      <c r="L36" s="4"/>
+      <c r="M36" s="4"/>
       <c r="N36" s="4"/>
       <c r="O36" s="4">
         <v>3</v>
@@ -2304,33 +2711,33 @@
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="4">
-        <v>3310</v>
+        <v>3134</v>
       </c>
       <c r="B37" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="C37" s="4">
+        <v>1</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F37" s="4" t="s">
         <v>86</v>
-      </c>
-      <c r="C37" s="4">
-        <v>1</v>
-      </c>
-      <c r="D37" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="E37" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="F37" s="4" t="s">
-        <v>88</v>
       </c>
       <c r="G37" s="4"/>
       <c r="H37" s="4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="I37" s="4"/>
       <c r="J37" s="4">
-        <v>200</v>
+        <v>3</v>
       </c>
       <c r="K37" s="4">
-        <v>250</v>
+        <v>40</v>
       </c>
       <c r="L37" s="4"/>
       <c r="M37" s="4"/>
@@ -2341,33 +2748,33 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="4">
-        <v>3311</v>
+        <v>3135</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C38" s="4">
         <v>2</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F38" s="4" t="s">
         <v>88</v>
       </c>
       <c r="G38" s="4"/>
       <c r="H38" s="4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="I38" s="4"/>
       <c r="J38" s="4">
-        <v>3000</v>
+        <v>7</v>
       </c>
       <c r="K38" s="4">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="L38" s="4"/>
       <c r="M38" s="4"/>
@@ -2378,33 +2785,33 @@
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="4">
-        <v>3312</v>
+        <v>3136</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C39" s="4">
         <v>3</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G39" s="4"/>
       <c r="H39" s="4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="I39" s="4"/>
       <c r="J39" s="4">
-        <v>20000</v>
+        <v>14</v>
       </c>
       <c r="K39" s="4">
-        <v>5000</v>
+        <v>120</v>
       </c>
       <c r="L39" s="4"/>
       <c r="M39" s="4"/>
@@ -2415,144 +2822,144 @@
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="4">
-        <v>3313</v>
+        <v>3137</v>
       </c>
       <c r="B40" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="C40" s="4">
+        <v>4</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F40" s="4" t="s">
         <v>90</v>
-      </c>
-      <c r="C40" s="4">
-        <v>1</v>
-      </c>
-      <c r="D40" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="E40" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="F40" s="4" t="s">
-        <v>92</v>
       </c>
       <c r="G40" s="4"/>
       <c r="H40" s="4" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="I40" s="4"/>
       <c r="J40" s="4">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="K40" s="4">
-        <v>250</v>
+        <v>205</v>
       </c>
       <c r="L40" s="4"/>
       <c r="M40" s="4"/>
       <c r="N40" s="4"/>
       <c r="O40" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="4">
-        <v>3314</v>
+        <v>3138</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="C41" s="4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="E41" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F41" s="4" t="s">
         <v>91</v>
-      </c>
-      <c r="F41" s="4" t="s">
-        <v>92</v>
       </c>
       <c r="G41" s="4"/>
       <c r="H41" s="4" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="I41" s="4"/>
       <c r="J41" s="4">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="K41" s="4">
-        <v>1000</v>
+        <v>350</v>
       </c>
       <c r="L41" s="4"/>
       <c r="M41" s="4"/>
       <c r="N41" s="4"/>
       <c r="O41" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="4">
-        <v>3315</v>
+        <v>3139</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="C42" s="4">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="F42" s="4" t="s">
         <v>92</v>
       </c>
       <c r="G42" s="4"/>
       <c r="H42" s="4" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="I42" s="4"/>
       <c r="J42" s="4">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="K42" s="4">
-        <v>5000</v>
+        <v>600</v>
       </c>
       <c r="L42" s="4"/>
       <c r="M42" s="4"/>
       <c r="N42" s="4"/>
       <c r="O42" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="4">
-        <v>3401</v>
+        <v>3201</v>
       </c>
       <c r="B43" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C43" s="4">
+        <v>1</v>
+      </c>
+      <c r="D43" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="C43" s="4">
-        <v>1</v>
-      </c>
-      <c r="D43" s="4" t="s">
+      <c r="E43" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="E43" s="4" t="s">
+      <c r="F43" s="4" t="s">
         <v>96</v>
-      </c>
-      <c r="F43" s="4" t="s">
-        <v>97</v>
       </c>
       <c r="G43" s="4"/>
       <c r="H43" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I43" s="4"/>
       <c r="J43" s="4">
-        <v>2000</v>
+        <v>1</v>
       </c>
       <c r="K43" s="4">
-        <v>300</v>
+        <v>80</v>
       </c>
       <c r="L43" s="4"/>
       <c r="M43" s="4"/>
@@ -2563,33 +2970,33 @@
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="4">
-        <v>3402</v>
+        <v>3202</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C44" s="4">
         <v>2</v>
       </c>
       <c r="D44" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E44" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="E44" s="4" t="s">
-        <v>96</v>
-      </c>
       <c r="F44" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G44" s="4"/>
       <c r="H44" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I44" s="4"/>
       <c r="J44" s="4">
-        <v>50000</v>
+        <v>3</v>
       </c>
       <c r="K44" s="4">
-        <v>1200</v>
+        <v>135</v>
       </c>
       <c r="L44" s="4"/>
       <c r="M44" s="4"/>
@@ -2600,40 +3007,36 @@
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="4">
-        <v>3403</v>
+        <v>3203</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C45" s="4">
         <v>3</v>
       </c>
       <c r="D45" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E45" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="E45" s="4" t="s">
-        <v>96</v>
-      </c>
       <c r="F45" s="4" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="G45" s="4"/>
       <c r="H45" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I45" s="4"/>
       <c r="J45" s="4">
-        <v>300000</v>
+        <v>5</v>
       </c>
       <c r="K45" s="4">
-        <v>5000</v>
-      </c>
-      <c r="L45" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="M45" s="4">
-        <v>10</v>
-      </c>
+        <v>220</v>
+      </c>
+      <c r="L45" s="4"/>
+      <c r="M45" s="4"/>
       <c r="N45" s="4"/>
       <c r="O45" s="4">
         <v>1</v>
@@ -2641,118 +3044,122 @@
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="4">
-        <v>3404</v>
+        <v>3204</v>
       </c>
       <c r="B46" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C46" s="4">
+        <v>4</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E46" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="F46" s="4" t="s">
         <v>100</v>
-      </c>
-      <c r="C46" s="4">
-        <v>1</v>
-      </c>
-      <c r="D46" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="E46" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="F46" s="4" t="s">
-        <v>102</v>
       </c>
       <c r="G46" s="4"/>
       <c r="H46" s="4" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="I46" s="4"/>
       <c r="J46" s="4">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="K46" s="4">
-        <v>300</v>
+        <v>365</v>
       </c>
       <c r="L46" s="4"/>
       <c r="M46" s="4"/>
       <c r="N46" s="4"/>
       <c r="O46" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="4">
-        <v>3405</v>
+        <v>3205</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="C47" s="4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D47" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E47" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="E47" s="4" t="s">
+      <c r="F47" s="4" t="s">
         <v>101</v>
-      </c>
-      <c r="F47" s="4" t="s">
-        <v>102</v>
       </c>
       <c r="G47" s="4"/>
       <c r="H47" s="4" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="I47" s="4"/>
       <c r="J47" s="4">
-        <v>30000</v>
+        <v>20</v>
       </c>
       <c r="K47" s="4">
-        <v>1200</v>
+        <v>605</v>
       </c>
       <c r="L47" s="4"/>
       <c r="M47" s="4"/>
       <c r="N47" s="4"/>
       <c r="O47" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="4">
-        <v>3406</v>
+        <v>3206</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="C48" s="4">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D48" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E48" s="4" t="s">
         <v>95</v>
-      </c>
-      <c r="E48" s="4" t="s">
-        <v>101</v>
       </c>
       <c r="F48" s="4" t="s">
         <v>102</v>
       </c>
       <c r="G48" s="4"/>
       <c r="H48" s="4" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="I48" s="4"/>
       <c r="J48" s="4">
-        <v>150000</v>
+        <v>50</v>
       </c>
       <c r="K48" s="4">
-        <v>5000</v>
-      </c>
-      <c r="L48" s="4"/>
-      <c r="M48" s="4"/>
+        <v>1000</v>
+      </c>
+      <c r="L48" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="M48" s="4">
+        <v>50</v>
+      </c>
       <c r="N48" s="4"/>
       <c r="O48" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="4">
-        <v>3407</v>
+        <v>3207</v>
       </c>
       <c r="B49" s="4" t="s">
         <v>104</v>
@@ -2761,7 +3168,7 @@
         <v>1</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E49" s="4" t="s">
         <v>105</v>
@@ -2773,23 +3180,25 @@
       <c r="H49" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="I49" s="4"/>
+      <c r="I49" s="4" t="s">
+        <v>108</v>
+      </c>
       <c r="J49" s="4">
-        <v>300</v>
+        <v>3</v>
       </c>
       <c r="K49" s="4">
-        <v>300</v>
+        <v>60</v>
       </c>
       <c r="L49" s="4"/>
       <c r="M49" s="4"/>
       <c r="N49" s="4"/>
       <c r="O49" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" s="4">
-        <v>3408</v>
+        <v>3208</v>
       </c>
       <c r="B50" s="4" t="s">
         <v>104</v>
@@ -2798,35 +3207,37 @@
         <v>2</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E50" s="4" t="s">
         <v>105</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="G50" s="4"/>
       <c r="H50" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="I50" s="4"/>
+      <c r="I50" s="4" t="s">
+        <v>110</v>
+      </c>
       <c r="J50" s="4">
-        <v>800</v>
+        <v>5</v>
       </c>
       <c r="K50" s="4">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="L50" s="4"/>
       <c r="M50" s="4"/>
       <c r="N50" s="4"/>
       <c r="O50" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="4">
-        <v>3409</v>
+        <v>3209</v>
       </c>
       <c r="B51" s="4" t="s">
         <v>104</v>
@@ -2835,513 +3246,519 @@
         <v>3</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E51" s="4" t="s">
         <v>105</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="G51" s="4"/>
       <c r="H51" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="I51" s="4"/>
+      <c r="I51" s="4" t="s">
+        <v>112</v>
+      </c>
       <c r="J51" s="4">
-        <v>1500</v>
+        <v>8</v>
       </c>
       <c r="K51" s="4">
-        <v>4000</v>
+        <v>165</v>
       </c>
       <c r="L51" s="4"/>
       <c r="M51" s="4"/>
       <c r="N51" s="4"/>
       <c r="O51" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="4">
-        <v>3410</v>
+        <v>3210</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C52" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="G52" s="4"/>
       <c r="H52" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="I52" s="4"/>
+        <v>107</v>
+      </c>
+      <c r="I52" s="4" t="s">
+        <v>62</v>
+      </c>
       <c r="J52" s="4">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="K52" s="4">
-        <v>300</v>
+        <v>270</v>
       </c>
       <c r="L52" s="4"/>
       <c r="M52" s="4"/>
       <c r="N52" s="4"/>
       <c r="O52" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="4">
-        <v>3411</v>
+        <v>3211</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C53" s="4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="G53" s="4"/>
       <c r="H53" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="I53" s="4"/>
+        <v>107</v>
+      </c>
+      <c r="I53" s="4" t="s">
+        <v>115</v>
+      </c>
       <c r="J53" s="4">
-        <v>300</v>
+        <v>15</v>
       </c>
       <c r="K53" s="4">
-        <v>1200</v>
+        <v>440</v>
       </c>
       <c r="L53" s="4"/>
       <c r="M53" s="4"/>
       <c r="N53" s="4"/>
       <c r="O53" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="4">
-        <v>3412</v>
+        <v>3212</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C54" s="4">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="G54" s="4"/>
       <c r="H54" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="I54" s="4"/>
+        <v>107</v>
+      </c>
+      <c r="I54" s="4" t="s">
+        <v>117</v>
+      </c>
       <c r="J54" s="4">
-        <v>1500</v>
+        <v>18</v>
       </c>
       <c r="K54" s="4">
-        <v>5000</v>
-      </c>
-      <c r="L54" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="M54" s="4">
-        <v>1</v>
-      </c>
+        <v>730</v>
+      </c>
+      <c r="L54" s="4"/>
+      <c r="M54" s="4"/>
       <c r="N54" s="4"/>
       <c r="O54" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="4">
-        <v>3501</v>
+        <v>3213</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="C55" s="4">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="G55" s="4"/>
       <c r="H55" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="I55" s="4"/>
+        <v>107</v>
+      </c>
+      <c r="I55" s="4" t="s">
+        <v>64</v>
+      </c>
       <c r="J55" s="4">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="K55" s="4">
-        <v>400</v>
-      </c>
-      <c r="L55" s="4"/>
-      <c r="M55" s="4"/>
+        <v>1200</v>
+      </c>
+      <c r="L55" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="M55" s="4">
+        <v>1</v>
+      </c>
       <c r="N55" s="4"/>
       <c r="O55" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="4">
-        <v>3502</v>
+        <v>3214</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C56" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="G56" s="4"/>
       <c r="H56" s="4" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="I56" s="4"/>
       <c r="J56" s="4">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="K56" s="4">
-        <v>1500</v>
+        <v>80</v>
       </c>
       <c r="L56" s="4"/>
       <c r="M56" s="4"/>
       <c r="N56" s="4"/>
       <c r="O56" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="4">
-        <v>3503</v>
+        <v>3215</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C57" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="G57" s="4"/>
       <c r="H57" s="4" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="I57" s="4"/>
       <c r="J57" s="4">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="K57" s="4">
-        <v>6000</v>
-      </c>
-      <c r="L57" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="M57" s="4">
-        <v>1</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="L57" s="4"/>
+      <c r="M57" s="4"/>
       <c r="N57" s="4"/>
       <c r="O57" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="4">
-        <v>3504</v>
+        <v>3216</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C58" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="G58" s="4"/>
       <c r="H58" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I58" s="4"/>
       <c r="J58" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K58" s="4">
-        <v>400</v>
+        <v>235</v>
       </c>
       <c r="L58" s="4"/>
       <c r="M58" s="4"/>
       <c r="N58" s="4"/>
       <c r="O58" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="4">
-        <v>3505</v>
+        <v>3217</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C59" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="G59" s="4"/>
       <c r="H59" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I59" s="4"/>
       <c r="J59" s="4">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K59" s="4">
-        <v>1500</v>
+        <v>405</v>
       </c>
       <c r="L59" s="4"/>
       <c r="M59" s="4"/>
       <c r="N59" s="4"/>
       <c r="O59" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" s="4">
-        <v>3506</v>
+        <v>3218</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C60" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="G60" s="4"/>
       <c r="H60" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I60" s="4"/>
       <c r="J60" s="4">
         <v>20</v>
       </c>
       <c r="K60" s="4">
-        <v>6000</v>
+        <v>700</v>
       </c>
       <c r="L60" s="4"/>
       <c r="M60" s="4"/>
       <c r="N60" s="4"/>
       <c r="O60" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" s="4">
-        <v>3507</v>
+        <v>3219</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="C61" s="4">
         <v>1</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="G61" s="4"/>
       <c r="H61" s="4" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="I61" s="4"/>
       <c r="J61" s="4">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="K61" s="4">
-        <v>400</v>
+        <v>80</v>
       </c>
       <c r="L61" s="4"/>
       <c r="M61" s="4"/>
       <c r="N61" s="4"/>
       <c r="O61" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" s="4">
-        <v>3508</v>
+        <v>3220</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="C62" s="4">
         <v>2</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="G62" s="4"/>
       <c r="H62" s="4" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="I62" s="4"/>
       <c r="J62" s="4">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="K62" s="4">
-        <v>1500</v>
+        <v>140</v>
       </c>
       <c r="L62" s="4"/>
       <c r="M62" s="4"/>
       <c r="N62" s="4"/>
       <c r="O62" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" s="4">
-        <v>3509</v>
+        <v>3221</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="C63" s="4">
         <v>3</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="G63" s="4"/>
       <c r="H63" s="4" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="I63" s="4"/>
       <c r="J63" s="4">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="K63" s="4">
-        <v>6000</v>
+        <v>235</v>
       </c>
       <c r="L63" s="4"/>
       <c r="M63" s="4"/>
       <c r="N63" s="4"/>
       <c r="O63" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" s="4">
-        <v>3510</v>
+        <v>3222</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C64" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="G64" s="4"/>
       <c r="H64" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I64" s="4"/>
       <c r="J64" s="4">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="K64" s="4">
-        <v>300</v>
+        <v>405</v>
       </c>
       <c r="L64" s="4"/>
       <c r="M64" s="4"/>
@@ -3352,33 +3769,33 @@
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" s="4">
-        <v>3511</v>
+        <v>3223</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C65" s="4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="G65" s="4"/>
       <c r="H65" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I65" s="4"/>
       <c r="J65" s="4">
-        <v>300</v>
+        <v>20</v>
       </c>
       <c r="K65" s="4">
-        <v>1200</v>
+        <v>700</v>
       </c>
       <c r="L65" s="4"/>
       <c r="M65" s="4"/>
@@ -3389,180 +3806,170 @@
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" s="4">
-        <v>3512</v>
+        <v>3301</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="C66" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>114</v>
+        <v>137</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="G66" s="4"/>
       <c r="H66" s="4" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="I66" s="4"/>
       <c r="J66" s="4">
-        <v>1200</v>
+        <v>3000</v>
       </c>
       <c r="K66" s="4">
-        <v>5000</v>
+        <v>60</v>
       </c>
       <c r="L66" s="4"/>
       <c r="M66" s="4"/>
       <c r="N66" s="4"/>
       <c r="O66" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" s="4">
-        <v>3601</v>
+        <v>3302</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="C67" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="G67" s="4"/>
       <c r="H67" s="4" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="I67" s="4"/>
       <c r="J67" s="4">
-        <v>1</v>
+        <v>12000</v>
       </c>
       <c r="K67" s="4">
-        <v>500</v>
+        <v>110</v>
       </c>
       <c r="L67" s="4"/>
       <c r="M67" s="4"/>
-      <c r="N67" s="4">
-        <v>1</v>
-      </c>
+      <c r="N67" s="4"/>
       <c r="O67" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" s="4">
-        <v>3602</v>
+        <v>3303</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="C68" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="G68" s="4"/>
       <c r="H68" s="4" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="I68" s="4"/>
       <c r="J68" s="4">
-        <v>3</v>
+        <v>30000</v>
       </c>
       <c r="K68" s="4">
-        <v>2000</v>
+        <v>200</v>
       </c>
       <c r="L68" s="4"/>
       <c r="M68" s="4"/>
-      <c r="N68" s="4">
-        <v>1</v>
-      </c>
+      <c r="N68" s="4"/>
       <c r="O68" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" s="4">
-        <v>3603</v>
+        <v>3304</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="C69" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="G69" s="4"/>
       <c r="H69" s="4" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="I69" s="4"/>
       <c r="J69" s="4">
-        <v>10</v>
+        <v>60000</v>
       </c>
       <c r="K69" s="4">
-        <v>8000</v>
-      </c>
-      <c r="L69" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="M69" s="4">
-        <v>1</v>
-      </c>
-      <c r="N69" s="4">
-        <v>1</v>
-      </c>
+        <v>360</v>
+      </c>
+      <c r="L69" s="4"/>
+      <c r="M69" s="4"/>
+      <c r="N69" s="4"/>
       <c r="O69" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" s="4">
-        <v>3604</v>
+        <v>3305</v>
       </c>
       <c r="B70" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="C70" s="4">
+        <v>5</v>
+      </c>
+      <c r="D70" s="4" t="s">
         <v>137</v>
-      </c>
-      <c r="C70" s="4">
-        <v>1</v>
-      </c>
-      <c r="D70" s="4" t="s">
-        <v>132</v>
       </c>
       <c r="E70" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="G70" s="4"/>
       <c r="H70" s="4" t="s">
@@ -3570,38 +3977,36 @@
       </c>
       <c r="I70" s="4"/>
       <c r="J70" s="4">
-        <v>1</v>
+        <v>100000</v>
       </c>
       <c r="K70" s="4">
-        <v>500</v>
+        <v>660</v>
       </c>
       <c r="L70" s="4"/>
       <c r="M70" s="4"/>
-      <c r="N70" s="4">
-        <v>1</v>
-      </c>
+      <c r="N70" s="4"/>
       <c r="O70" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" s="4">
-        <v>3605</v>
+        <v>3306</v>
       </c>
       <c r="B71" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="C71" s="4">
+        <v>6</v>
+      </c>
+      <c r="D71" s="4" t="s">
         <v>137</v>
-      </c>
-      <c r="C71" s="4">
-        <v>2</v>
-      </c>
-      <c r="D71" s="4" t="s">
-        <v>132</v>
       </c>
       <c r="E71" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="G71" s="4"/>
       <c r="H71" s="4" t="s">
@@ -3609,303 +4014,3310 @@
       </c>
       <c r="I71" s="4"/>
       <c r="J71" s="4">
-        <v>3</v>
+        <v>160000</v>
       </c>
       <c r="K71" s="4">
-        <v>2000</v>
-      </c>
-      <c r="L71" s="4"/>
-      <c r="M71" s="4"/>
-      <c r="N71" s="4">
-        <v>1</v>
-      </c>
+        <v>1200</v>
+      </c>
+      <c r="L71" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="M71" s="4">
+        <v>10</v>
+      </c>
+      <c r="N71" s="4"/>
       <c r="O71" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72" s="4">
-        <v>3606</v>
+        <v>3307</v>
       </c>
       <c r="B72" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="C72" s="4">
+        <v>1</v>
+      </c>
+      <c r="D72" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="C72" s="4">
-        <v>3</v>
-      </c>
-      <c r="D72" s="4" t="s">
-        <v>132</v>
-      </c>
       <c r="E72" s="4" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="G72" s="4"/>
       <c r="H72" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="I72" s="4"/>
+        <v>150</v>
+      </c>
+      <c r="I72" s="4" t="s">
+        <v>151</v>
+      </c>
       <c r="J72" s="4">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K72" s="4">
-        <v>8000</v>
+        <v>50</v>
       </c>
       <c r="L72" s="4"/>
       <c r="M72" s="4"/>
-      <c r="N72" s="4">
-        <v>1</v>
-      </c>
+      <c r="N72" s="4"/>
       <c r="O72" s="4">
         <v>2</v>
       </c>
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73" s="4">
-        <v>3607</v>
+        <v>3308</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="C73" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="G73" s="4"/>
       <c r="H73" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="I73" s="4"/>
+        <v>150</v>
+      </c>
+      <c r="I73" s="4" t="s">
+        <v>153</v>
+      </c>
       <c r="J73" s="4">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K73" s="4">
-        <v>500</v>
+        <v>80</v>
       </c>
       <c r="L73" s="4"/>
       <c r="M73" s="4"/>
-      <c r="N73" s="4">
-        <v>1</v>
-      </c>
+      <c r="N73" s="4"/>
       <c r="O73" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74" s="4">
-        <v>3608</v>
+        <v>3309</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="C74" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="G74" s="4"/>
       <c r="H74" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="I74" s="4"/>
+        <v>150</v>
+      </c>
+      <c r="I74" s="4" t="s">
+        <v>155</v>
+      </c>
       <c r="J74" s="4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K74" s="4">
-        <v>2000</v>
+        <v>135</v>
       </c>
       <c r="L74" s="4"/>
       <c r="M74" s="4"/>
-      <c r="N74" s="4">
-        <v>1</v>
-      </c>
+      <c r="N74" s="4"/>
       <c r="O74" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" s="4">
-        <v>3609</v>
+        <v>3310</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="C75" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="G75" s="4"/>
       <c r="H75" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="I75" s="4"/>
+        <v>150</v>
+      </c>
+      <c r="I75" s="4" t="s">
+        <v>157</v>
+      </c>
       <c r="J75" s="4">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="K75" s="4">
-        <v>8000</v>
+        <v>220</v>
       </c>
       <c r="L75" s="4"/>
       <c r="M75" s="4"/>
-      <c r="N75" s="4">
-        <v>1</v>
-      </c>
+      <c r="N75" s="4"/>
       <c r="O75" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76" s="4">
-        <v>3610</v>
+        <v>3311</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C76" s="4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="G76" s="4"/>
       <c r="H76" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="I76" s="4"/>
+        <v>150</v>
+      </c>
+      <c r="I76" s="4" t="s">
+        <v>159</v>
+      </c>
       <c r="J76" s="4">
-        <v>300</v>
+        <v>15</v>
       </c>
       <c r="K76" s="4">
-        <v>500</v>
+        <v>365</v>
       </c>
       <c r="L76" s="4"/>
       <c r="M76" s="4"/>
-      <c r="N76" s="4">
-        <v>1</v>
-      </c>
+      <c r="N76" s="4"/>
       <c r="O76" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A77" s="4">
-        <v>3611</v>
+        <v>3312</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C77" s="4">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="G77" s="4"/>
       <c r="H77" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="I77" s="4"/>
+        <v>150</v>
+      </c>
+      <c r="I77" s="4" t="s">
+        <v>161</v>
+      </c>
       <c r="J77" s="4">
+        <v>20</v>
+      </c>
+      <c r="K77" s="4">
         <v>600</v>
-      </c>
-      <c r="K77" s="4">
-        <v>2000</v>
       </c>
       <c r="L77" s="4"/>
       <c r="M77" s="4"/>
-      <c r="N77" s="4">
-        <v>1</v>
-      </c>
+      <c r="N77" s="4"/>
       <c r="O77" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A78" s="4">
-        <v>3612</v>
+        <v>3313</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="C78" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="G78" s="4"/>
       <c r="H78" s="4" t="s">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="I78" s="4"/>
       <c r="J78" s="4">
-        <v>1050</v>
+        <v>1000000</v>
       </c>
       <c r="K78" s="4">
-        <v>8000</v>
+        <v>60</v>
       </c>
       <c r="L78" s="4"/>
       <c r="M78" s="4"/>
-      <c r="N78" s="4">
-        <v>1</v>
-      </c>
+      <c r="N78" s="4"/>
       <c r="O78" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A79" s="4">
+        <v>3314</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="C79" s="4">
+        <v>2</v>
+      </c>
+      <c r="D79" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="E79" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="F79" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="G79" s="4"/>
+      <c r="H79" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="I79" s="4"/>
+      <c r="J79" s="4">
+        <v>3000000</v>
+      </c>
+      <c r="K79" s="4">
+        <v>130</v>
+      </c>
+      <c r="L79" s="4"/>
+      <c r="M79" s="4"/>
+      <c r="N79" s="4"/>
+      <c r="O79" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="80" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A80" s="4">
+        <v>3315</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="C80" s="4">
+        <v>3</v>
+      </c>
+      <c r="D80" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="E80" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="F80" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="G80" s="4"/>
+      <c r="H80" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="I80" s="4"/>
+      <c r="J80" s="4">
+        <v>8000000</v>
+      </c>
+      <c r="K80" s="4">
+        <v>290</v>
+      </c>
+      <c r="L80" s="4"/>
+      <c r="M80" s="4"/>
+      <c r="N80" s="4"/>
+      <c r="O80" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A81" s="4">
+        <v>3316</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="C81" s="4">
+        <v>4</v>
+      </c>
+      <c r="D81" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="E81" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="F81" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="G81" s="4"/>
+      <c r="H81" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="I81" s="4"/>
+      <c r="J81" s="4">
+        <v>18000000</v>
+      </c>
+      <c r="K81" s="4">
+        <v>635</v>
+      </c>
+      <c r="L81" s="4"/>
+      <c r="M81" s="4"/>
+      <c r="N81" s="4"/>
+      <c r="O81" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A82" s="4">
+        <v>3317</v>
+      </c>
+      <c r="B82" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="C82" s="4">
+        <v>5</v>
+      </c>
+      <c r="D82" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="E82" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="F82" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="G82" s="4"/>
+      <c r="H82" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="I82" s="4"/>
+      <c r="J82" s="4">
+        <v>35000000</v>
+      </c>
+      <c r="K82" s="4">
+        <v>1400</v>
+      </c>
+      <c r="L82" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="M82" s="4">
+        <v>10</v>
+      </c>
+      <c r="N82" s="4"/>
+      <c r="O82" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="83" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A83" s="4">
+        <v>3318</v>
+      </c>
+      <c r="B83" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="C83" s="4">
+        <v>1</v>
+      </c>
+      <c r="D83" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="E83" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="F83" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="G83" s="4"/>
+      <c r="H83" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="I83" s="4"/>
+      <c r="J83" s="4">
+        <v>500</v>
+      </c>
+      <c r="K83" s="4">
+        <v>50</v>
+      </c>
+      <c r="L83" s="4"/>
+      <c r="M83" s="4"/>
+      <c r="N83" s="4"/>
+      <c r="O83" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A84" s="4">
+        <v>3319</v>
+      </c>
+      <c r="B84" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="C84" s="4">
+        <v>2</v>
+      </c>
+      <c r="D84" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="E84" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="F84" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="G84" s="4"/>
+      <c r="H84" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="I84" s="4"/>
+      <c r="J84" s="4">
+        <v>2500</v>
+      </c>
+      <c r="K84" s="4">
+        <v>95</v>
+      </c>
+      <c r="L84" s="4"/>
+      <c r="M84" s="4"/>
+      <c r="N84" s="4"/>
+      <c r="O84" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="85" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A85" s="4">
+        <v>3320</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="C85" s="4">
+        <v>3</v>
+      </c>
+      <c r="D85" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="E85" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="F85" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="G85" s="4"/>
+      <c r="H85" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="I85" s="4"/>
+      <c r="J85" s="4">
+        <v>8000</v>
+      </c>
+      <c r="K85" s="4">
+        <v>175</v>
+      </c>
+      <c r="L85" s="4"/>
+      <c r="M85" s="4"/>
+      <c r="N85" s="4"/>
+      <c r="O85" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="86" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A86" s="4">
+        <v>3321</v>
+      </c>
+      <c r="B86" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="C86" s="4">
+        <v>4</v>
+      </c>
+      <c r="D86" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="E86" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="F86" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="G86" s="4"/>
+      <c r="H86" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="I86" s="4"/>
+      <c r="J86" s="4">
+        <v>20000</v>
+      </c>
+      <c r="K86" s="4">
+        <v>320</v>
+      </c>
+      <c r="L86" s="4"/>
+      <c r="M86" s="4"/>
+      <c r="N86" s="4"/>
+      <c r="O86" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="87" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A87" s="4">
+        <v>3322</v>
+      </c>
+      <c r="B87" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="C87" s="4">
+        <v>5</v>
+      </c>
+      <c r="D87" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="E87" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="F87" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="G87" s="4"/>
+      <c r="H87" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="I87" s="4"/>
+      <c r="J87" s="4">
+        <v>45000</v>
+      </c>
+      <c r="K87" s="4">
+        <v>600</v>
+      </c>
+      <c r="L87" s="4"/>
+      <c r="M87" s="4"/>
+      <c r="N87" s="4"/>
+      <c r="O87" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="88" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A88" s="4">
+        <v>3323</v>
+      </c>
+      <c r="B88" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="C88" s="4">
+        <v>1</v>
+      </c>
+      <c r="D88" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="E88" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="F88" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="G88" s="4"/>
+      <c r="H88" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="I88" s="4"/>
+      <c r="J88" s="4">
+        <v>10</v>
+      </c>
+      <c r="K88" s="4">
+        <v>50</v>
+      </c>
+      <c r="L88" s="4"/>
+      <c r="M88" s="4"/>
+      <c r="N88" s="4"/>
+      <c r="O88" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="89" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A89" s="4">
+        <v>3324</v>
+      </c>
+      <c r="B89" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="C89" s="4">
+        <v>2</v>
+      </c>
+      <c r="D89" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="E89" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="F89" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="G89" s="4"/>
+      <c r="H89" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="I89" s="4"/>
+      <c r="J89" s="4">
+        <v>30</v>
+      </c>
+      <c r="K89" s="4">
+        <v>90</v>
+      </c>
+      <c r="L89" s="4"/>
+      <c r="M89" s="4"/>
+      <c r="N89" s="4"/>
+      <c r="O89" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A90" s="4">
+        <v>3325</v>
+      </c>
+      <c r="B90" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="C90" s="4">
+        <v>3</v>
+      </c>
+      <c r="D90" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="E90" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="F90" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="G90" s="4"/>
+      <c r="H90" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="I90" s="4"/>
+      <c r="J90" s="4">
+        <v>100</v>
+      </c>
+      <c r="K90" s="4">
+        <v>160</v>
+      </c>
+      <c r="L90" s="4"/>
+      <c r="M90" s="4"/>
+      <c r="N90" s="4"/>
+      <c r="O90" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="91" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A91" s="4">
+        <v>3326</v>
+      </c>
+      <c r="B91" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="C91" s="4">
+        <v>4</v>
+      </c>
+      <c r="D91" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="E91" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="F91" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="G91" s="4"/>
+      <c r="H91" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="I91" s="4"/>
+      <c r="J91" s="4">
+        <v>300</v>
+      </c>
+      <c r="K91" s="4">
+        <v>280</v>
+      </c>
+      <c r="L91" s="4"/>
+      <c r="M91" s="4"/>
+      <c r="N91" s="4"/>
+      <c r="O91" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A92" s="4">
+        <v>3327</v>
+      </c>
+      <c r="B92" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="C92" s="4">
+        <v>5</v>
+      </c>
+      <c r="D92" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="E92" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="F92" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="G92" s="4"/>
+      <c r="H92" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="I92" s="4"/>
+      <c r="J92" s="4">
+        <v>600</v>
+      </c>
+      <c r="K92" s="4">
+        <v>500</v>
+      </c>
+      <c r="L92" s="4"/>
+      <c r="M92" s="4"/>
+      <c r="N92" s="4"/>
+      <c r="O92" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="93" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A93" s="4">
+        <v>3401</v>
+      </c>
+      <c r="B93" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="C93" s="4">
+        <v>1</v>
+      </c>
+      <c r="D93" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="E93" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="F93" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="G93" s="4"/>
+      <c r="H93" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="I93" s="4"/>
+      <c r="J93" s="4">
+        <v>20000</v>
+      </c>
+      <c r="K93" s="4">
+        <v>60</v>
+      </c>
+      <c r="L93" s="4"/>
+      <c r="M93" s="4"/>
+      <c r="N93" s="4"/>
+      <c r="O93" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A94" s="4">
+        <v>3402</v>
+      </c>
+      <c r="B94" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="C94" s="4">
+        <v>2</v>
+      </c>
+      <c r="D94" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="E94" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="F94" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="G94" s="4"/>
+      <c r="H94" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="I94" s="4"/>
+      <c r="J94" s="4">
+        <v>100000</v>
+      </c>
+      <c r="K94" s="4">
+        <v>120</v>
+      </c>
+      <c r="L94" s="4"/>
+      <c r="M94" s="4"/>
+      <c r="N94" s="4"/>
+      <c r="O94" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A95" s="4">
+        <v>3403</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="C95" s="4">
+        <v>3</v>
+      </c>
+      <c r="D95" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="E95" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="F95" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="G95" s="4"/>
+      <c r="H95" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="I95" s="4"/>
+      <c r="J95" s="4">
+        <v>300000</v>
+      </c>
+      <c r="K95" s="4">
+        <v>245</v>
+      </c>
+      <c r="L95" s="4"/>
+      <c r="M95" s="4"/>
+      <c r="N95" s="4"/>
+      <c r="O95" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A96" s="4">
+        <v>3404</v>
+      </c>
+      <c r="B96" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="C96" s="4">
+        <v>4</v>
+      </c>
+      <c r="D96" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="E96" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="F96" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="G96" s="4"/>
+      <c r="H96" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="I96" s="4"/>
+      <c r="J96" s="4">
+        <v>600000</v>
+      </c>
+      <c r="K96" s="4">
+        <v>495</v>
+      </c>
+      <c r="L96" s="4"/>
+      <c r="M96" s="4"/>
+      <c r="N96" s="4"/>
+      <c r="O96" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A97" s="4">
+        <v>3405</v>
+      </c>
+      <c r="B97" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="C97" s="4">
+        <v>5</v>
+      </c>
+      <c r="D97" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="E97" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="F97" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="G97" s="4"/>
+      <c r="H97" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="I97" s="4"/>
+      <c r="J97" s="4">
+        <v>1000000</v>
+      </c>
+      <c r="K97" s="4">
+        <v>1000</v>
+      </c>
+      <c r="L97" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="M97" s="4">
+        <v>10</v>
+      </c>
+      <c r="N97" s="4"/>
+      <c r="O97" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A98" s="4">
+        <v>3406</v>
+      </c>
+      <c r="B98" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="C98" s="4">
+        <v>1</v>
+      </c>
+      <c r="D98" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="E98" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="F98" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="G98" s="4"/>
+      <c r="H98" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="I98" s="4"/>
+      <c r="J98" s="4">
+        <v>15000</v>
+      </c>
+      <c r="K98" s="4">
+        <v>50</v>
+      </c>
+      <c r="L98" s="4"/>
+      <c r="M98" s="4"/>
+      <c r="N98" s="4"/>
+      <c r="O98" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="99" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A99" s="4">
+        <v>3407</v>
+      </c>
+      <c r="B99" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="C99" s="4">
+        <v>2</v>
+      </c>
+      <c r="D99" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="E99" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="F99" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="G99" s="4"/>
+      <c r="H99" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="I99" s="4"/>
+      <c r="J99" s="4">
+        <v>80000</v>
+      </c>
+      <c r="K99" s="4">
+        <v>95</v>
+      </c>
+      <c r="L99" s="4"/>
+      <c r="M99" s="4"/>
+      <c r="N99" s="4"/>
+      <c r="O99" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="100" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A100" s="4">
+        <v>3408</v>
+      </c>
+      <c r="B100" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="C100" s="4">
+        <v>3</v>
+      </c>
+      <c r="D100" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="E100" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="F100" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="G100" s="4"/>
+      <c r="H100" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="I100" s="4"/>
+      <c r="J100" s="4">
+        <v>250000</v>
+      </c>
+      <c r="K100" s="4">
+        <v>175</v>
+      </c>
+      <c r="L100" s="4"/>
+      <c r="M100" s="4"/>
+      <c r="N100" s="4"/>
+      <c r="O100" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="101" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A101" s="4">
+        <v>3409</v>
+      </c>
+      <c r="B101" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="C101" s="4">
+        <v>4</v>
+      </c>
+      <c r="D101" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="E101" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="F101" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="G101" s="4"/>
+      <c r="H101" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="I101" s="4"/>
+      <c r="J101" s="4">
+        <v>500000</v>
+      </c>
+      <c r="K101" s="4">
+        <v>320</v>
+      </c>
+      <c r="L101" s="4"/>
+      <c r="M101" s="4"/>
+      <c r="N101" s="4"/>
+      <c r="O101" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="102" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A102" s="4">
+        <v>3410</v>
+      </c>
+      <c r="B102" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="C102" s="4">
+        <v>5</v>
+      </c>
+      <c r="D102" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="E102" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="F102" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="G102" s="4"/>
+      <c r="H102" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="I102" s="4"/>
+      <c r="J102" s="4">
+        <v>900000</v>
+      </c>
+      <c r="K102" s="4">
+        <v>600</v>
+      </c>
+      <c r="L102" s="4"/>
+      <c r="M102" s="4"/>
+      <c r="N102" s="4"/>
+      <c r="O102" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="103" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A103" s="4">
+        <v>3411</v>
+      </c>
+      <c r="B103" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="C103" s="4">
+        <v>1</v>
+      </c>
+      <c r="D103" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="E103" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="F103" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="G103" s="4"/>
+      <c r="H103" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="I103" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="J103" s="4">
+        <v>3</v>
+      </c>
+      <c r="K103" s="4">
+        <v>50</v>
+      </c>
+      <c r="L103" s="4"/>
+      <c r="M103" s="4"/>
+      <c r="N103" s="4"/>
+      <c r="O103" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="104" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A104" s="4">
+        <v>3412</v>
+      </c>
+      <c r="B104" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="C104" s="4">
+        <v>2</v>
+      </c>
+      <c r="D104" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="E104" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="F104" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="G104" s="4"/>
+      <c r="H104" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="I104" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="J104" s="4">
+        <v>5</v>
+      </c>
+      <c r="K104" s="4">
+        <v>90</v>
+      </c>
+      <c r="L104" s="4"/>
+      <c r="M104" s="4"/>
+      <c r="N104" s="4"/>
+      <c r="O104" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="105" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A105" s="4">
+        <v>3413</v>
+      </c>
+      <c r="B105" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="C105" s="4">
+        <v>3</v>
+      </c>
+      <c r="D105" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="E105" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="F105" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="G105" s="4"/>
+      <c r="H105" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="I105" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="J105" s="4">
+        <v>8</v>
+      </c>
+      <c r="K105" s="4">
+        <v>160</v>
+      </c>
+      <c r="L105" s="4"/>
+      <c r="M105" s="4"/>
+      <c r="N105" s="4"/>
+      <c r="O105" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="106" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A106" s="4">
+        <v>3414</v>
+      </c>
+      <c r="B106" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="C106" s="4">
+        <v>4</v>
+      </c>
+      <c r="D106" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="E106" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="F106" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="G106" s="4"/>
+      <c r="H106" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="I106" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="J106" s="4">
+        <v>12</v>
+      </c>
+      <c r="K106" s="4">
+        <v>280</v>
+      </c>
+      <c r="L106" s="4"/>
+      <c r="M106" s="4"/>
+      <c r="N106" s="4"/>
+      <c r="O106" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="107" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A107" s="4">
+        <v>3415</v>
+      </c>
+      <c r="B107" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="C107" s="4">
+        <v>5</v>
+      </c>
+      <c r="D107" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="E107" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="F107" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="G107" s="4"/>
+      <c r="H107" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="I107" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="J107" s="4">
+        <v>15</v>
+      </c>
+      <c r="K107" s="4">
+        <v>500</v>
+      </c>
+      <c r="L107" s="4"/>
+      <c r="M107" s="4"/>
+      <c r="N107" s="4"/>
+      <c r="O107" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="108" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A108" s="4">
+        <v>3416</v>
+      </c>
+      <c r="B108" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="C108" s="4">
+        <v>1</v>
+      </c>
+      <c r="D108" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="E108" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="F108" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="G108" s="4"/>
+      <c r="H108" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="I108" s="4"/>
+      <c r="J108" s="4">
+        <v>50</v>
+      </c>
+      <c r="K108" s="4">
+        <v>60</v>
+      </c>
+      <c r="L108" s="4"/>
+      <c r="M108" s="4"/>
+      <c r="N108" s="4"/>
+      <c r="O108" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="109" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A109" s="4">
+        <v>3417</v>
+      </c>
+      <c r="B109" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="C109" s="4">
+        <v>2</v>
+      </c>
+      <c r="D109" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="E109" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="F109" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="G109" s="4"/>
+      <c r="H109" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="I109" s="4"/>
+      <c r="J109" s="4">
+        <v>250</v>
+      </c>
+      <c r="K109" s="4">
+        <v>120</v>
+      </c>
+      <c r="L109" s="4"/>
+      <c r="M109" s="4"/>
+      <c r="N109" s="4"/>
+      <c r="O109" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="110" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A110" s="4">
+        <v>3418</v>
+      </c>
+      <c r="B110" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="C110" s="4">
+        <v>3</v>
+      </c>
+      <c r="D110" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="E110" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="F110" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="G110" s="4"/>
+      <c r="H110" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="I110" s="4"/>
+      <c r="J110" s="4">
+        <v>800</v>
+      </c>
+      <c r="K110" s="4">
+        <v>230</v>
+      </c>
+      <c r="L110" s="4"/>
+      <c r="M110" s="4"/>
+      <c r="N110" s="4"/>
+      <c r="O110" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="111" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A111" s="4">
+        <v>3419</v>
+      </c>
+      <c r="B111" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="C111" s="4">
+        <v>4</v>
+      </c>
+      <c r="D111" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="E111" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="F111" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="G111" s="4"/>
+      <c r="H111" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="I111" s="4"/>
+      <c r="J111" s="4">
+        <v>1800</v>
+      </c>
+      <c r="K111" s="4">
+        <v>455</v>
+      </c>
+      <c r="L111" s="4"/>
+      <c r="M111" s="4"/>
+      <c r="N111" s="4"/>
+      <c r="O111" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="112" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A112" s="4">
+        <v>3420</v>
+      </c>
+      <c r="B112" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="C112" s="4">
+        <v>5</v>
+      </c>
+      <c r="D112" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="E112" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="F112" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="G112" s="4"/>
+      <c r="H112" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="I112" s="4"/>
+      <c r="J112" s="4">
+        <v>3000</v>
+      </c>
+      <c r="K112" s="4">
+        <v>900</v>
+      </c>
+      <c r="L112" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="M112" s="4">
+        <v>1</v>
+      </c>
+      <c r="N112" s="4"/>
+      <c r="O112" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="113" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A113" s="4">
+        <v>3501</v>
+      </c>
+      <c r="B113" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="C113" s="4">
+        <v>1</v>
+      </c>
+      <c r="D113" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="E113" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="F113" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="G113" s="4"/>
+      <c r="H113" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="I113" s="4"/>
+      <c r="J113" s="4">
+        <v>10</v>
+      </c>
+      <c r="K113" s="4">
+        <v>80</v>
+      </c>
+      <c r="L113" s="4"/>
+      <c r="M113" s="4"/>
+      <c r="N113" s="4"/>
+      <c r="O113" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A114" s="4">
+        <v>3502</v>
+      </c>
+      <c r="B114" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="C114" s="4">
+        <v>2</v>
+      </c>
+      <c r="D114" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="E114" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="F114" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="G114" s="4"/>
+      <c r="H114" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="I114" s="4"/>
+      <c r="J114" s="4">
+        <v>25</v>
+      </c>
+      <c r="K114" s="4">
+        <v>125</v>
+      </c>
+      <c r="L114" s="4"/>
+      <c r="M114" s="4"/>
+      <c r="N114" s="4"/>
+      <c r="O114" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A115" s="4">
+        <v>3503</v>
+      </c>
+      <c r="B115" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="C115" s="4">
+        <v>3</v>
+      </c>
+      <c r="D115" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="E115" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="F115" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="G115" s="4"/>
+      <c r="H115" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="I115" s="4"/>
+      <c r="J115" s="4">
+        <v>50</v>
+      </c>
+      <c r="K115" s="4">
+        <v>195</v>
+      </c>
+      <c r="L115" s="4"/>
+      <c r="M115" s="4"/>
+      <c r="N115" s="4"/>
+      <c r="O115" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A116" s="4">
+        <v>3504</v>
+      </c>
+      <c r="B116" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="C116" s="4">
+        <v>4</v>
+      </c>
+      <c r="D116" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="E116" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="F116" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="G116" s="4"/>
+      <c r="H116" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="I116" s="4"/>
+      <c r="J116" s="4">
+        <v>90</v>
+      </c>
+      <c r="K116" s="4">
+        <v>310</v>
+      </c>
+      <c r="L116" s="4"/>
+      <c r="M116" s="4"/>
+      <c r="N116" s="4"/>
+      <c r="O116" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A117" s="4">
+        <v>3505</v>
+      </c>
+      <c r="B117" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="C117" s="4">
+        <v>5</v>
+      </c>
+      <c r="D117" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="E117" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="F117" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="G117" s="4"/>
+      <c r="H117" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="I117" s="4"/>
+      <c r="J117" s="4">
+        <v>140</v>
+      </c>
+      <c r="K117" s="4">
+        <v>485</v>
+      </c>
+      <c r="L117" s="4"/>
+      <c r="M117" s="4"/>
+      <c r="N117" s="4"/>
+      <c r="O117" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A118" s="4">
+        <v>3506</v>
+      </c>
+      <c r="B118" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="C118" s="4">
+        <v>6</v>
+      </c>
+      <c r="D118" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="E118" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="F118" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="G118" s="4"/>
+      <c r="H118" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="I118" s="4"/>
+      <c r="J118" s="4">
+        <v>200</v>
+      </c>
+      <c r="K118" s="4">
+        <v>765</v>
+      </c>
+      <c r="L118" s="4"/>
+      <c r="M118" s="4"/>
+      <c r="N118" s="4"/>
+      <c r="O118" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A119" s="4">
+        <v>3507</v>
+      </c>
+      <c r="B119" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="C119" s="4">
+        <v>7</v>
+      </c>
+      <c r="D119" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="E119" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="F119" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="G119" s="4"/>
+      <c r="H119" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="I119" s="4"/>
+      <c r="J119" s="4">
+        <v>268</v>
+      </c>
+      <c r="K119" s="4">
+        <v>1200</v>
+      </c>
+      <c r="L119" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="M119" s="4">
+        <v>1</v>
+      </c>
+      <c r="N119" s="4"/>
+      <c r="O119" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A120" s="4">
+        <v>3508</v>
+      </c>
+      <c r="B120" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="C120" s="4">
+        <v>1</v>
+      </c>
+      <c r="D120" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="E120" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="F120" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="G120" s="4"/>
+      <c r="H120" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="I120" s="4"/>
+      <c r="J120" s="4">
+        <v>5</v>
+      </c>
+      <c r="K120" s="4">
+        <v>70</v>
+      </c>
+      <c r="L120" s="4"/>
+      <c r="M120" s="4"/>
+      <c r="N120" s="4"/>
+      <c r="O120" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="121" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A121" s="4">
+        <v>3509</v>
+      </c>
+      <c r="B121" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="C121" s="4">
+        <v>2</v>
+      </c>
+      <c r="D121" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="E121" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="F121" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="G121" s="4"/>
+      <c r="H121" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="I121" s="4"/>
+      <c r="J121" s="4">
+        <v>8</v>
+      </c>
+      <c r="K121" s="4">
+        <v>115</v>
+      </c>
+      <c r="L121" s="4"/>
+      <c r="M121" s="4"/>
+      <c r="N121" s="4"/>
+      <c r="O121" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="122" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A122" s="4">
+        <v>3510</v>
+      </c>
+      <c r="B122" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="C122" s="4">
+        <v>3</v>
+      </c>
+      <c r="D122" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="E122" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="F122" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="G122" s="4"/>
+      <c r="H122" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="I122" s="4"/>
+      <c r="J122" s="4">
+        <v>11</v>
+      </c>
+      <c r="K122" s="4">
+        <v>195</v>
+      </c>
+      <c r="L122" s="4"/>
+      <c r="M122" s="4"/>
+      <c r="N122" s="4"/>
+      <c r="O122" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="123" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A123" s="4">
+        <v>3511</v>
+      </c>
+      <c r="B123" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="C123" s="4">
+        <v>4</v>
+      </c>
+      <c r="D123" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="E123" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="F123" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="G123" s="4"/>
+      <c r="H123" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="I123" s="4"/>
+      <c r="J123" s="4">
+        <v>14</v>
+      </c>
+      <c r="K123" s="4">
+        <v>325</v>
+      </c>
+      <c r="L123" s="4"/>
+      <c r="M123" s="4"/>
+      <c r="N123" s="4"/>
+      <c r="O123" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="124" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A124" s="4">
+        <v>3512</v>
+      </c>
+      <c r="B124" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="C124" s="4">
+        <v>5</v>
+      </c>
+      <c r="D124" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="E124" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="F124" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="G124" s="4"/>
+      <c r="H124" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="I124" s="4"/>
+      <c r="J124" s="4">
+        <v>17</v>
+      </c>
+      <c r="K124" s="4">
+        <v>540</v>
+      </c>
+      <c r="L124" s="4"/>
+      <c r="M124" s="4"/>
+      <c r="N124" s="4"/>
+      <c r="O124" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="125" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A125" s="4">
+        <v>3513</v>
+      </c>
+      <c r="B125" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="C125" s="4">
+        <v>6</v>
+      </c>
+      <c r="D125" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="E125" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="F125" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="G125" s="4"/>
+      <c r="H125" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="I125" s="4"/>
+      <c r="J125" s="4">
+        <v>19</v>
+      </c>
+      <c r="K125" s="4">
+        <v>900</v>
+      </c>
+      <c r="L125" s="4"/>
+      <c r="M125" s="4"/>
+      <c r="N125" s="4"/>
+      <c r="O125" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="126" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A126" s="4">
+        <v>3514</v>
+      </c>
+      <c r="B126" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="C126" s="4">
+        <v>1</v>
+      </c>
+      <c r="D126" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="E126" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="F126" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="G126" s="4"/>
+      <c r="H126" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="I126" s="4"/>
+      <c r="J126" s="4">
+        <v>5</v>
+      </c>
+      <c r="K126" s="4">
+        <v>70</v>
+      </c>
+      <c r="L126" s="4"/>
+      <c r="M126" s="4"/>
+      <c r="N126" s="4"/>
+      <c r="O126" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="127" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A127" s="4">
+        <v>3515</v>
+      </c>
+      <c r="B127" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="C127" s="4">
+        <v>2</v>
+      </c>
+      <c r="D127" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="E127" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="F127" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="G127" s="4"/>
+      <c r="H127" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="I127" s="4"/>
+      <c r="J127" s="4">
+        <v>10</v>
+      </c>
+      <c r="K127" s="4">
+        <v>115</v>
+      </c>
+      <c r="L127" s="4"/>
+      <c r="M127" s="4"/>
+      <c r="N127" s="4"/>
+      <c r="O127" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="128" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A128" s="4">
+        <v>3516</v>
+      </c>
+      <c r="B128" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="C128" s="4">
+        <v>3</v>
+      </c>
+      <c r="D128" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="E128" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="F128" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="G128" s="4"/>
+      <c r="H128" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="I128" s="4"/>
+      <c r="J128" s="4">
+        <v>15</v>
+      </c>
+      <c r="K128" s="4">
+        <v>195</v>
+      </c>
+      <c r="L128" s="4"/>
+      <c r="M128" s="4"/>
+      <c r="N128" s="4"/>
+      <c r="O128" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="129" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A129" s="4">
+        <v>3517</v>
+      </c>
+      <c r="B129" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="C129" s="4">
+        <v>4</v>
+      </c>
+      <c r="D129" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="E129" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="F129" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="G129" s="4"/>
+      <c r="H129" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="I129" s="4"/>
+      <c r="J129" s="4">
+        <v>20</v>
+      </c>
+      <c r="K129" s="4">
+        <v>325</v>
+      </c>
+      <c r="L129" s="4"/>
+      <c r="M129" s="4"/>
+      <c r="N129" s="4"/>
+      <c r="O129" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="130" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A130" s="4">
+        <v>3518</v>
+      </c>
+      <c r="B130" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="C130" s="4">
+        <v>5</v>
+      </c>
+      <c r="D130" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="E130" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="F130" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="G130" s="4"/>
+      <c r="H130" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="I130" s="4"/>
+      <c r="J130" s="4">
+        <v>25</v>
+      </c>
+      <c r="K130" s="4">
+        <v>540</v>
+      </c>
+      <c r="L130" s="4"/>
+      <c r="M130" s="4"/>
+      <c r="N130" s="4"/>
+      <c r="O130" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="131" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A131" s="4">
+        <v>3519</v>
+      </c>
+      <c r="B131" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="C131" s="4">
+        <v>6</v>
+      </c>
+      <c r="D131" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="E131" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="F131" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="G131" s="4"/>
+      <c r="H131" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="I131" s="4"/>
+      <c r="J131" s="4">
+        <v>31</v>
+      </c>
+      <c r="K131" s="4">
+        <v>900</v>
+      </c>
+      <c r="L131" s="4"/>
+      <c r="M131" s="4"/>
+      <c r="N131" s="4"/>
+      <c r="O131" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="132" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A132" s="4">
+        <v>3520</v>
+      </c>
+      <c r="B132" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="C132" s="4">
+        <v>1</v>
+      </c>
+      <c r="D132" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="E132" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="F132" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="G132" s="4"/>
+      <c r="H132" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="I132" s="4"/>
+      <c r="J132" s="4">
+        <v>100</v>
+      </c>
+      <c r="K132" s="4">
+        <v>50</v>
+      </c>
+      <c r="L132" s="4"/>
+      <c r="M132" s="4"/>
+      <c r="N132" s="4"/>
+      <c r="O132" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="133" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A133" s="4">
+        <v>3521</v>
+      </c>
+      <c r="B133" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="C133" s="4">
+        <v>2</v>
+      </c>
+      <c r="D133" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="E133" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="F133" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="G133" s="4"/>
+      <c r="H133" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="I133" s="4"/>
+      <c r="J133" s="4">
+        <v>400</v>
+      </c>
+      <c r="K133" s="4">
+        <v>90</v>
+      </c>
+      <c r="L133" s="4"/>
+      <c r="M133" s="4"/>
+      <c r="N133" s="4"/>
+      <c r="O133" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="134" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A134" s="4">
+        <v>3522</v>
+      </c>
+      <c r="B134" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="C134" s="4">
+        <v>3</v>
+      </c>
+      <c r="D134" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="E134" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="F134" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="G134" s="4"/>
+      <c r="H134" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="I134" s="4"/>
+      <c r="J134" s="4">
+        <v>900</v>
+      </c>
+      <c r="K134" s="4">
+        <v>160</v>
+      </c>
+      <c r="L134" s="4"/>
+      <c r="M134" s="4"/>
+      <c r="N134" s="4"/>
+      <c r="O134" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="135" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A135" s="4">
+        <v>3523</v>
+      </c>
+      <c r="B135" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="C135" s="4">
+        <v>4</v>
+      </c>
+      <c r="D135" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="E135" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="F135" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="G135" s="4"/>
+      <c r="H135" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="I135" s="4"/>
+      <c r="J135" s="4">
+        <v>1800</v>
+      </c>
+      <c r="K135" s="4">
+        <v>280</v>
+      </c>
+      <c r="L135" s="4"/>
+      <c r="M135" s="4"/>
+      <c r="N135" s="4"/>
+      <c r="O135" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="136" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A136" s="4">
+        <v>3524</v>
+      </c>
+      <c r="B136" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="C136" s="4">
+        <v>5</v>
+      </c>
+      <c r="D136" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="E136" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="F136" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="G136" s="4"/>
+      <c r="H136" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="I136" s="4"/>
+      <c r="J136" s="4">
+        <v>3000</v>
+      </c>
+      <c r="K136" s="4">
+        <v>500</v>
+      </c>
+      <c r="L136" s="4"/>
+      <c r="M136" s="4"/>
+      <c r="N136" s="4"/>
+      <c r="O136" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="137" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A137" s="4">
+        <v>3601</v>
+      </c>
+      <c r="B137" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="C137" s="4">
+        <v>1</v>
+      </c>
+      <c r="D137" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="E137" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="F137" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="G137" s="4"/>
+      <c r="H137" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="I137" s="4"/>
+      <c r="J137" s="4">
+        <v>1</v>
+      </c>
+      <c r="K137" s="4">
+        <v>100</v>
+      </c>
+      <c r="L137" s="4"/>
+      <c r="M137" s="4"/>
+      <c r="N137" s="4">
+        <v>1</v>
+      </c>
+      <c r="O137" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A138" s="4">
+        <v>3602</v>
+      </c>
+      <c r="B138" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="C138" s="4">
+        <v>2</v>
+      </c>
+      <c r="D138" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="E138" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="F138" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="G138" s="4"/>
+      <c r="H138" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="I138" s="4"/>
+      <c r="J138" s="4">
+        <v>3</v>
+      </c>
+      <c r="K138" s="4">
+        <v>195</v>
+      </c>
+      <c r="L138" s="4"/>
+      <c r="M138" s="4"/>
+      <c r="N138" s="4">
+        <v>1</v>
+      </c>
+      <c r="O138" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A139" s="4">
+        <v>3603</v>
+      </c>
+      <c r="B139" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="C139" s="4">
+        <v>3</v>
+      </c>
+      <c r="D139" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="E139" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="F139" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="G139" s="4"/>
+      <c r="H139" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="I139" s="4"/>
+      <c r="J139" s="4">
+        <v>6</v>
+      </c>
+      <c r="K139" s="4">
+        <v>385</v>
+      </c>
+      <c r="L139" s="4"/>
+      <c r="M139" s="4"/>
+      <c r="N139" s="4">
+        <v>1</v>
+      </c>
+      <c r="O139" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A140" s="4">
+        <v>3604</v>
+      </c>
+      <c r="B140" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="C140" s="4">
+        <v>4</v>
+      </c>
+      <c r="D140" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="E140" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="F140" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="G140" s="4"/>
+      <c r="H140" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="I140" s="4"/>
+      <c r="J140" s="4">
+        <v>10</v>
+      </c>
+      <c r="K140" s="4">
+        <v>760</v>
+      </c>
+      <c r="L140" s="4"/>
+      <c r="M140" s="4"/>
+      <c r="N140" s="4">
+        <v>1</v>
+      </c>
+      <c r="O140" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A141" s="4">
+        <v>3605</v>
+      </c>
+      <c r="B141" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="C141" s="4">
+        <v>5</v>
+      </c>
+      <c r="D141" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="E141" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="F141" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="G141" s="4"/>
+      <c r="H141" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="I141" s="4"/>
+      <c r="J141" s="4">
+        <v>20</v>
+      </c>
+      <c r="K141" s="4">
+        <v>1500</v>
+      </c>
+      <c r="L141" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="M141" s="4">
+        <v>1</v>
+      </c>
+      <c r="N141" s="4">
+        <v>1</v>
+      </c>
+      <c r="O141" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A142" s="4">
+        <v>3606</v>
+      </c>
+      <c r="B142" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="C142" s="4">
+        <v>1</v>
+      </c>
+      <c r="D142" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="E142" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="F142" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="G142" s="4"/>
+      <c r="H142" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="I142" s="4"/>
+      <c r="J142" s="4">
+        <v>1</v>
+      </c>
+      <c r="K142" s="4">
+        <v>100</v>
+      </c>
+      <c r="L142" s="4"/>
+      <c r="M142" s="4"/>
+      <c r="N142" s="4">
+        <v>1</v>
+      </c>
+      <c r="O142" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="143" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A143" s="4">
+        <v>3607</v>
+      </c>
+      <c r="B143" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="C143" s="4">
+        <v>2</v>
+      </c>
+      <c r="D143" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="E143" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="F143" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="G143" s="4"/>
+      <c r="H143" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="I143" s="4"/>
+      <c r="J143" s="4">
+        <v>3</v>
+      </c>
+      <c r="K143" s="4">
+        <v>185</v>
+      </c>
+      <c r="L143" s="4"/>
+      <c r="M143" s="4"/>
+      <c r="N143" s="4">
+        <v>1</v>
+      </c>
+      <c r="O143" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="144" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A144" s="4">
+        <v>3608</v>
+      </c>
+      <c r="B144" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="C144" s="4">
+        <v>3</v>
+      </c>
+      <c r="D144" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="E144" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="F144" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="G144" s="4"/>
+      <c r="H144" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="I144" s="4"/>
+      <c r="J144" s="4">
+        <v>6</v>
+      </c>
+      <c r="K144" s="4">
+        <v>345</v>
+      </c>
+      <c r="L144" s="4"/>
+      <c r="M144" s="4"/>
+      <c r="N144" s="4">
+        <v>1</v>
+      </c>
+      <c r="O144" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="145" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A145" s="4">
+        <v>3609</v>
+      </c>
+      <c r="B145" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="C145" s="4">
+        <v>4</v>
+      </c>
+      <c r="D145" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="E145" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="F145" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="G145" s="4"/>
+      <c r="H145" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="I145" s="4"/>
+      <c r="J145" s="4">
+        <v>10</v>
+      </c>
+      <c r="K145" s="4">
+        <v>645</v>
+      </c>
+      <c r="L145" s="4"/>
+      <c r="M145" s="4"/>
+      <c r="N145" s="4">
+        <v>1</v>
+      </c>
+      <c r="O145" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="146" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A146" s="4">
+        <v>3610</v>
+      </c>
+      <c r="B146" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="C146" s="4">
+        <v>5</v>
+      </c>
+      <c r="D146" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="E146" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="F146" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="G146" s="4"/>
+      <c r="H146" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="I146" s="4"/>
+      <c r="J146" s="4">
+        <v>20</v>
+      </c>
+      <c r="K146" s="4">
+        <v>1200</v>
+      </c>
+      <c r="L146" s="4"/>
+      <c r="M146" s="4"/>
+      <c r="N146" s="4">
+        <v>1</v>
+      </c>
+      <c r="O146" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="147" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A147" s="4">
+        <v>3611</v>
+      </c>
+      <c r="B147" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="C147" s="4">
+        <v>1</v>
+      </c>
+      <c r="D147" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="E147" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="F147" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="G147" s="4"/>
+      <c r="H147" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="I147" s="4"/>
+      <c r="J147" s="4">
+        <v>1</v>
+      </c>
+      <c r="K147" s="4">
+        <v>100</v>
+      </c>
+      <c r="L147" s="4"/>
+      <c r="M147" s="4"/>
+      <c r="N147" s="4">
+        <v>1</v>
+      </c>
+      <c r="O147" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="148" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A148" s="4">
+        <v>3612</v>
+      </c>
+      <c r="B148" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="C148" s="4">
+        <v>2</v>
+      </c>
+      <c r="D148" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="E148" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="F148" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="G148" s="4"/>
+      <c r="H148" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="I148" s="4"/>
+      <c r="J148" s="4">
+        <v>3</v>
+      </c>
+      <c r="K148" s="4">
+        <v>185</v>
+      </c>
+      <c r="L148" s="4"/>
+      <c r="M148" s="4"/>
+      <c r="N148" s="4">
+        <v>1</v>
+      </c>
+      <c r="O148" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="149" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A149" s="4">
+        <v>3613</v>
+      </c>
+      <c r="B149" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="C149" s="4">
+        <v>3</v>
+      </c>
+      <c r="D149" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="E149" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="F149" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="G149" s="4"/>
+      <c r="H149" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="I149" s="4"/>
+      <c r="J149" s="4">
+        <v>6</v>
+      </c>
+      <c r="K149" s="4">
+        <v>345</v>
+      </c>
+      <c r="L149" s="4"/>
+      <c r="M149" s="4"/>
+      <c r="N149" s="4">
+        <v>1</v>
+      </c>
+      <c r="O149" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="150" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A150" s="4">
+        <v>3614</v>
+      </c>
+      <c r="B150" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="C150" s="4">
+        <v>4</v>
+      </c>
+      <c r="D150" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="E150" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="F150" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="G150" s="4"/>
+      <c r="H150" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="I150" s="4"/>
+      <c r="J150" s="4">
+        <v>10</v>
+      </c>
+      <c r="K150" s="4">
+        <v>645</v>
+      </c>
+      <c r="L150" s="4"/>
+      <c r="M150" s="4"/>
+      <c r="N150" s="4">
+        <v>1</v>
+      </c>
+      <c r="O150" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="151" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A151" s="4">
+        <v>3615</v>
+      </c>
+      <c r="B151" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="C151" s="4">
+        <v>5</v>
+      </c>
+      <c r="D151" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="E151" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="F151" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="G151" s="4"/>
+      <c r="H151" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="I151" s="4"/>
+      <c r="J151" s="4">
+        <v>20</v>
+      </c>
+      <c r="K151" s="4">
+        <v>1200</v>
+      </c>
+      <c r="L151" s="4"/>
+      <c r="M151" s="4"/>
+      <c r="N151" s="4">
+        <v>1</v>
+      </c>
+      <c r="O151" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="152" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A152" s="4">
+        <v>3616</v>
+      </c>
+      <c r="B152" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="C152" s="4">
+        <v>1</v>
+      </c>
+      <c r="D152" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="E152" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="F152" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="G152" s="4"/>
+      <c r="H152" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="I152" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="J152" s="4">
+        <v>3</v>
+      </c>
+      <c r="K152" s="4">
+        <v>100</v>
+      </c>
+      <c r="L152" s="4"/>
+      <c r="M152" s="4"/>
+      <c r="N152" s="4">
+        <v>1</v>
+      </c>
+      <c r="O152" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="153" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A153" s="4">
+        <v>3617</v>
+      </c>
+      <c r="B153" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="C153" s="4">
+        <v>2</v>
+      </c>
+      <c r="D153" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="E153" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="F153" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="G153" s="4"/>
+      <c r="H153" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="I153" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="J153" s="4">
+        <v>5</v>
+      </c>
+      <c r="K153" s="4">
+        <v>170</v>
+      </c>
+      <c r="L153" s="4"/>
+      <c r="M153" s="4"/>
+      <c r="N153" s="4">
+        <v>1</v>
+      </c>
+      <c r="O153" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="154" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A154" s="4">
+        <v>3618</v>
+      </c>
+      <c r="B154" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="C154" s="4">
+        <v>3</v>
+      </c>
+      <c r="D154" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="E154" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="F154" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="G154" s="4"/>
+      <c r="H154" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="I154" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="J154" s="4">
+        <v>8</v>
+      </c>
+      <c r="K154" s="4">
+        <v>295</v>
+      </c>
+      <c r="L154" s="4"/>
+      <c r="M154" s="4"/>
+      <c r="N154" s="4">
+        <v>1</v>
+      </c>
+      <c r="O154" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="155" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A155" s="4">
+        <v>3619</v>
+      </c>
+      <c r="B155" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="C155" s="4">
+        <v>4</v>
+      </c>
+      <c r="D155" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="E155" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="F155" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="G155" s="4"/>
+      <c r="H155" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="I155" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="J155" s="4">
+        <v>10</v>
+      </c>
+      <c r="K155" s="4">
+        <v>510</v>
+      </c>
+      <c r="L155" s="4"/>
+      <c r="M155" s="4"/>
+      <c r="N155" s="4">
+        <v>1</v>
+      </c>
+      <c r="O155" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="156" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A156" s="4">
+        <v>3620</v>
+      </c>
+      <c r="B156" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="C156" s="4">
+        <v>5</v>
+      </c>
+      <c r="D156" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="E156" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="F156" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="G156" s="4"/>
+      <c r="H156" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="I156" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="J156" s="4">
+        <v>12</v>
+      </c>
+      <c r="K156" s="4">
+        <v>875</v>
+      </c>
+      <c r="L156" s="4"/>
+      <c r="M156" s="4"/>
+      <c r="N156" s="4">
+        <v>1</v>
+      </c>
+      <c r="O156" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="157" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A157" s="4">
+        <v>3621</v>
+      </c>
+      <c r="B157" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="C157" s="4">
+        <v>6</v>
+      </c>
+      <c r="D157" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="E157" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="F157" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="G157" s="4"/>
+      <c r="H157" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="I157" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="J157" s="4">
+        <v>15</v>
+      </c>
+      <c r="K157" s="4">
+        <v>1500</v>
+      </c>
+      <c r="L157" s="4"/>
+      <c r="M157" s="4"/>
+      <c r="N157" s="4">
+        <v>1</v>
+      </c>
+      <c r="O157" s="4">
         <v>4</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="取值非法" error="只能是：level / stage / combat / economy / collect / challenge" sqref="D4:D178">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="取值非法" error="只能是：level / stage / combat / economy / collect / challenge" sqref="D4:D257">
       <formula1>"level,stage,combat,economy,collect,challenge"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="取值非法" error="只能是：login / play_games / victory / kill_enemies / gold_earned / spend_gold / relics_picked / skills_used / buffs_bought / stage_reached / hero_level / level_reached / level_up_count / login_streak / survive_time / kill_in_run / gold_in_run / clear_no_damage / clear_fast / clear_low_hp / run_no_relic_clear / clear_one_skill / damage_dealt / crit_hits / draw_count / relic_collected / buff_types / skills_picked" sqref="H4:H178">
-      <formula1>"login,play_games,victory,kill_enemies,gold_earned,spend_gold,relics_picked,skills_used,buffs_bought,stage_reached,hero_level,level_reached,level_up_count,login_streak,survive_time,kill_in_run,gold_in_run,clear_no_damage,clear_fast,clear_low_hp,run_no_relic_clear,clear_one_skill,damage_dealt,crit_hits,draw_count,relic_collected,buff_types,skills_picked"</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="取值非法" error="只能是：login / play_games / victory / kill_enemies / gold_earned / spend_gold / relics_picked / skills_used / buffs_bought / stage_reached / hero_level / level_reached / level_up_count / login_streak / survive_time / kill_in_run / gold_in_run / clear_no_damage / clear_fast / clear_low_hp / run_no_relic_clear / clear_one_skill / damage_dealt / crit_hits / draw_count / relic_collected / buff_types / skills_picked / run_stage / run_hero_level / run_kill / run_gold / run_survive" sqref="H4:H257">
+      <formula1>"login,play_games,victory,kill_enemies,gold_earned,spend_gold,relics_picked,skills_used,buffs_bought,stage_reached,hero_level,level_reached,level_up_count,login_streak,survive_time,kill_in_run,gold_in_run,clear_no_damage,clear_fast,clear_low_hp,run_no_relic_clear,clear_one_skill,damage_dealt,crit_hits,draw_count,relic_collected,buff_types,skills_picked,run_stage,run_hero_level,run_kill,run_gold,run_survive"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="取值非法" error="只能是：run_start_gold / shop_option_plus / shop_draw_discount / ad_free_draw / kill_buff_discount / gold_gain_bonus / battle_exp_bonus / hero_start_level / hero_select_free / relic_start_gift" sqref="L4:L178">
-      <formula1>"run_start_gold,shop_option_plus,shop_draw_discount,ad_free_draw,kill_buff_discount,gold_gain_bonus,battle_exp_bonus,hero_start_level,hero_select_free,relic_start_gift"</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="取值非法" error="只能是：run_start_gold / run_start_kill_points / shop_option_plus / shop_draw_discount / ad_free_draw / kill_buff_discount / gold_gain_bonus / battle_exp_bonus / hero_start_level / hero_select_free / relic_start_gift" sqref="L4:L257">
+      <formula1>"run_start_gold,run_start_kill_points,shop_option_plus,shop_draw_discount,ad_free_draw,kill_buff_discount,gold_gain_bonus,battle_exp_bonus,hero_start_level,hero_select_free,relic_start_gift"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
